--- a/gstdatabase/GSTR-1-2020-2021.xlsx
+++ b/gstdatabase/GSTR-1-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E03F15-DD43-4373-9614-188DAFDFA14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1D1DA9-464D-4CAC-AA87-0B1BDD82A706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -440,20 +440,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -469,6 +463,12 @@
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -767,13 +767,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -783,10 +783,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -813,107 +813,107 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="8" spans="1:62" s="26" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="36">
         <v>43922</v>
       </c>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="33">
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="32">
         <v>43952</v>
       </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="33">
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="32">
         <v>43983</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="33">
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="32">
         <v>44013</v>
       </c>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="33">
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="32">
         <v>44044</v>
       </c>
-      <c r="X8" s="34"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="33">
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="32">
         <v>44075</v>
       </c>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="33">
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="32">
         <v>44105</v>
       </c>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="34"/>
-      <c r="AL8" s="33">
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="32">
         <v>44136</v>
       </c>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="33">
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="32">
         <v>44166</v>
       </c>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="34"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="33">
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="32">
         <v>44197</v>
       </c>
-      <c r="AW8" s="34"/>
-      <c r="AX8" s="34"/>
-      <c r="AY8" s="34"/>
-      <c r="AZ8" s="34"/>
-      <c r="BA8" s="33">
+      <c r="AW8" s="33"/>
+      <c r="AX8" s="33"/>
+      <c r="AY8" s="33"/>
+      <c r="AZ8" s="33"/>
+      <c r="BA8" s="32">
         <v>44228</v>
       </c>
-      <c r="BB8" s="34"/>
-      <c r="BC8" s="34"/>
-      <c r="BD8" s="34"/>
-      <c r="BE8" s="34"/>
-      <c r="BF8" s="33">
+      <c r="BB8" s="33"/>
+      <c r="BC8" s="33"/>
+      <c r="BD8" s="33"/>
+      <c r="BE8" s="33"/>
+      <c r="BF8" s="32">
         <v>44256</v>
       </c>
-      <c r="BG8" s="34"/>
-      <c r="BH8" s="34"/>
-      <c r="BI8" s="34"/>
-      <c r="BJ8" s="34"/>
+      <c r="BG8" s="33"/>
+      <c r="BH8" s="33"/>
+      <c r="BI8" s="33"/>
+      <c r="BJ8" s="33"/>
     </row>
     <row r="9" spans="1:62" s="26" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="27" t="s">
         <v>4</v>
       </c>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="AD10" s="9">
         <f>AE10-AC10</f>
-        <v>41498</v>
+        <v>41500</v>
       </c>
       <c r="AE10" s="8">
-        <v>74584</v>
+        <v>74586</v>
       </c>
       <c r="AF10" s="10">
         <f>AE10/AB10</f>
-        <v>0.84388223846484578</v>
+        <v>0.84390486750695848</v>
       </c>
       <c r="AG10" s="5">
         <v>40367</v>
@@ -1212,14 +1212,14 @@
       </c>
       <c r="AI10" s="9">
         <f>AJ10-AH10</f>
-        <v>22879</v>
+        <v>22880</v>
       </c>
       <c r="AJ10" s="8">
-        <v>29168</v>
+        <v>29169</v>
       </c>
       <c r="AK10" s="10">
         <f>AJ10/AG10</f>
-        <v>0.72257041642926156</v>
+        <v>0.72259518913964382</v>
       </c>
       <c r="AL10" s="5">
         <v>37461</v>
@@ -1229,14 +1229,14 @@
       </c>
       <c r="AN10" s="9">
         <f>AO10-AM10</f>
-        <v>22126</v>
+        <v>22127</v>
       </c>
       <c r="AO10" s="8">
-        <v>29441</v>
+        <v>29442</v>
       </c>
       <c r="AP10" s="10">
         <f>AO10/AL10</f>
-        <v>0.78591068044099199</v>
+        <v>0.7859373748698647</v>
       </c>
       <c r="AQ10" s="22">
         <v>84627</v>
@@ -1246,14 +1246,14 @@
       </c>
       <c r="AS10" s="9">
         <f>AT10-AR10</f>
-        <v>27501</v>
+        <v>27503</v>
       </c>
       <c r="AT10" s="8">
-        <v>75888</v>
+        <v>75890</v>
       </c>
       <c r="AU10" s="10">
         <f>AT10/AQ10</f>
-        <v>0.89673508454748485</v>
+        <v>0.89675871766693849</v>
       </c>
       <c r="AV10" s="22">
         <v>45594</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AX10" s="9">
         <f>AY10-AW10</f>
-        <v>27131</v>
+        <v>27132</v>
       </c>
       <c r="AY10" s="9">
-        <v>39604</v>
+        <v>39605</v>
       </c>
       <c r="AZ10" s="10">
         <f>AY10/AV10</f>
-        <v>0.86862306443830328</v>
+        <v>0.86864499714874766</v>
       </c>
       <c r="BA10" s="22">
         <v>44931</v>
@@ -1280,14 +1280,14 @@
       </c>
       <c r="BC10" s="9">
         <f>BD10-BB10</f>
-        <v>26089</v>
+        <v>26090</v>
       </c>
       <c r="BD10" s="8">
-        <v>40407</v>
+        <v>40408</v>
       </c>
       <c r="BE10" s="10">
         <f>BD10/BA10</f>
-        <v>0.89931227882753551</v>
+        <v>0.89933453517615902</v>
       </c>
       <c r="BF10" s="9">
         <v>84140</v>
@@ -1297,14 +1297,14 @@
       </c>
       <c r="BH10" s="9">
         <f>BI10-BG10</f>
-        <v>48794</v>
+        <v>48797</v>
       </c>
       <c r="BI10" s="6">
-        <v>78617</v>
+        <v>78620</v>
       </c>
       <c r="BJ10" s="10">
         <f>BI10/BF10</f>
-        <v>0.93435940099833614</v>
+        <v>0.93439505585928218</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="O11" s="9">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>40632</v>
+        <v>40633</v>
       </c>
       <c r="P11" s="8">
-        <v>78757</v>
+        <v>78758</v>
       </c>
       <c r="Q11" s="10">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.92324013832717899</v>
+        <v>0.92325186096946255</v>
       </c>
       <c r="R11" s="5">
         <v>34872</v>
@@ -1407,14 +1407,14 @@
       </c>
       <c r="AD11" s="9">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>27334</v>
+        <v>27335</v>
       </c>
       <c r="AE11" s="8">
-        <v>81753</v>
+        <v>81754</v>
       </c>
       <c r="AF11" s="10">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.91466771089729249</v>
+        <v>0.91467889908256883</v>
       </c>
       <c r="AG11" s="5">
         <v>29840</v>
@@ -1458,14 +1458,14 @@
       </c>
       <c r="AS11" s="9">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>16647</v>
+        <v>16649</v>
       </c>
       <c r="AT11" s="8">
-        <v>84384</v>
+        <v>84386</v>
       </c>
       <c r="AU11" s="10">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.92695037019135706</v>
+        <v>0.92697234000483331</v>
       </c>
       <c r="AV11" s="22">
         <v>40247</v>
@@ -1492,14 +1492,14 @@
       </c>
       <c r="BC11" s="9">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>17872</v>
+        <v>17873</v>
       </c>
       <c r="BD11" s="8">
-        <v>36088</v>
+        <v>36089</v>
       </c>
       <c r="BE11" s="10">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.90195196321011717</v>
+        <v>0.90197695633700736</v>
       </c>
       <c r="BF11" s="9">
         <v>90790</v>
@@ -1509,14 +1509,14 @@
       </c>
       <c r="BH11" s="9">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="BI11" s="6">
-        <v>87262</v>
+        <v>87263</v>
       </c>
       <c r="BJ11" s="10">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>0.96114109483423282</v>
+        <v>0.96115210926313466</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="J12" s="9">
         <f t="shared" si="2"/>
-        <v>19680</v>
+        <v>19681</v>
       </c>
       <c r="K12" s="8">
-        <v>87895</v>
+        <v>87896</v>
       </c>
       <c r="L12" s="10">
         <f t="shared" si="3"/>
-        <v>0.30700207124669493</v>
+        <v>0.30700556407417368</v>
       </c>
       <c r="M12" s="5">
         <v>312776</v>
@@ -1568,14 +1568,14 @@
       </c>
       <c r="O12" s="9">
         <f t="shared" si="4"/>
-        <v>124079</v>
+        <v>124080</v>
       </c>
       <c r="P12" s="8">
-        <v>286593</v>
+        <v>286594</v>
       </c>
       <c r="Q12" s="10">
         <f t="shared" si="5"/>
-        <v>0.9162883341432847</v>
+        <v>0.91629153131953855</v>
       </c>
       <c r="R12" s="5">
         <v>125200</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="T12" s="9">
         <f t="shared" si="6"/>
-        <v>51194</v>
+        <v>51195</v>
       </c>
       <c r="U12" s="8">
-        <v>88945</v>
+        <v>88946</v>
       </c>
       <c r="V12" s="10">
         <f t="shared" si="7"/>
-        <v>0.71042332268370612</v>
+        <v>0.71043130990415337</v>
       </c>
       <c r="W12" s="5">
         <v>120831</v>
@@ -1602,14 +1602,14 @@
       </c>
       <c r="Y12" s="9">
         <f t="shared" si="8"/>
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="Z12" s="8">
-        <v>89304</v>
+        <v>89305</v>
       </c>
       <c r="AA12" s="10">
         <f t="shared" si="9"/>
-        <v>0.73908185813243288</v>
+        <v>0.73909013415431468</v>
       </c>
       <c r="AB12" s="5">
         <v>318929</v>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="AD12" s="9">
         <f t="shared" si="10"/>
-        <v>87173</v>
+        <v>87174</v>
       </c>
       <c r="AE12" s="8">
-        <v>293221</v>
+        <v>293222</v>
       </c>
       <c r="AF12" s="10">
         <f t="shared" si="11"/>
-        <v>0.9193927175013874</v>
+        <v>0.91939585299549431</v>
       </c>
       <c r="AG12" s="5">
         <v>113974</v>
@@ -1636,14 +1636,14 @@
       </c>
       <c r="AI12" s="9">
         <f t="shared" si="12"/>
-        <v>42587</v>
+        <v>42588</v>
       </c>
       <c r="AJ12" s="8">
-        <v>89929</v>
+        <v>89930</v>
       </c>
       <c r="AK12" s="10">
         <f t="shared" si="13"/>
-        <v>0.78903083159317033</v>
+        <v>0.78903960552406693</v>
       </c>
       <c r="AL12" s="5">
         <v>111535</v>
@@ -1653,14 +1653,14 @@
       </c>
       <c r="AN12" s="9">
         <f t="shared" si="14"/>
-        <v>40539</v>
+        <v>40540</v>
       </c>
       <c r="AO12" s="8">
-        <v>90429</v>
+        <v>90430</v>
       </c>
       <c r="AP12" s="10">
         <f t="shared" si="15"/>
-        <v>0.81076792038373602</v>
+        <v>0.81077688617922627</v>
       </c>
       <c r="AQ12" s="22">
         <v>323550</v>
@@ -1670,14 +1670,14 @@
       </c>
       <c r="AS12" s="9">
         <f t="shared" si="16"/>
-        <v>38427</v>
+        <v>38430</v>
       </c>
       <c r="AT12" s="8">
-        <v>299681</v>
+        <v>299684</v>
       </c>
       <c r="AU12" s="10">
         <f t="shared" si="17"/>
-        <v>0.92622778550455875</v>
+        <v>0.92623705764178643</v>
       </c>
       <c r="AV12" s="22">
         <v>144846</v>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="AX12" s="9">
         <f t="shared" si="18"/>
-        <v>44873</v>
+        <v>44874</v>
       </c>
       <c r="AY12" s="9">
-        <v>126339</v>
+        <v>126340</v>
       </c>
       <c r="AZ12" s="10">
         <f t="shared" si="19"/>
-        <v>0.87222981649475995</v>
+        <v>0.87223672037888511</v>
       </c>
       <c r="BA12" s="22">
         <v>144289</v>
@@ -1704,14 +1704,14 @@
       </c>
       <c r="BC12" s="9">
         <f t="shared" si="20"/>
-        <v>40165</v>
+        <v>40166</v>
       </c>
       <c r="BD12" s="8">
-        <v>129018</v>
+        <v>129019</v>
       </c>
       <c r="BE12" s="10">
         <f t="shared" si="21"/>
-        <v>0.89416379626998588</v>
+        <v>0.89417072680523113</v>
       </c>
       <c r="BF12" s="9">
         <v>318519</v>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="BH12" s="9">
         <f t="shared" si="22"/>
-        <v>94440</v>
+        <v>94441</v>
       </c>
       <c r="BI12" s="6">
-        <v>304170</v>
+        <v>304171</v>
       </c>
       <c r="BJ12" s="10">
         <f t="shared" si="23"/>
-        <v>0.95495088205099221</v>
+        <v>0.95495402158113019</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>11306</v>
+        <v>11307</v>
       </c>
       <c r="F14" s="8">
-        <v>34691</v>
+        <v>34692</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="1"/>
-        <v>0.26455425913215891</v>
+        <v>0.26456188515213908</v>
       </c>
       <c r="H14" s="5">
         <v>113453</v>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="J14" s="9">
         <f t="shared" si="2"/>
-        <v>13248</v>
+        <v>13249</v>
       </c>
       <c r="K14" s="8">
-        <v>34877</v>
+        <v>34878</v>
       </c>
       <c r="L14" s="10">
         <f t="shared" si="3"/>
-        <v>0.30741364265378612</v>
+        <v>0.30742245687641578</v>
       </c>
       <c r="M14" s="5">
         <v>130093</v>
@@ -1992,14 +1992,14 @@
       </c>
       <c r="O14" s="9">
         <f t="shared" si="4"/>
-        <v>66720</v>
+        <v>66721</v>
       </c>
       <c r="P14" s="8">
-        <v>115533</v>
+        <v>115534</v>
       </c>
       <c r="Q14" s="10">
         <f t="shared" si="5"/>
-        <v>0.88808006579908216</v>
+        <v>0.88808775260774986</v>
       </c>
       <c r="R14" s="5">
         <v>63308</v>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="T14" s="9">
         <f t="shared" si="6"/>
-        <v>27586</v>
+        <v>27587</v>
       </c>
       <c r="U14" s="8">
-        <v>35699</v>
+        <v>35700</v>
       </c>
       <c r="V14" s="10">
         <f t="shared" si="7"/>
-        <v>0.56389397864408919</v>
+        <v>0.56390977443609025</v>
       </c>
       <c r="W14" s="5">
         <v>61226</v>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="Y14" s="9">
         <f t="shared" si="8"/>
-        <v>25506</v>
+        <v>25507</v>
       </c>
       <c r="Z14" s="8">
-        <v>36048</v>
+        <v>36049</v>
       </c>
       <c r="AA14" s="10">
         <f t="shared" si="9"/>
-        <v>0.58876947701956683</v>
+        <v>0.58878580995002128</v>
       </c>
       <c r="AB14" s="5">
         <v>138271</v>
@@ -2043,14 +2043,14 @@
       </c>
       <c r="AD14" s="9">
         <f t="shared" si="10"/>
-        <v>53076</v>
+        <v>53079</v>
       </c>
       <c r="AE14" s="8">
-        <v>120157</v>
+        <v>120160</v>
       </c>
       <c r="AF14" s="10">
         <f t="shared" si="11"/>
-        <v>0.86899639114492555</v>
+        <v>0.86901808766841926</v>
       </c>
       <c r="AG14" s="5">
         <v>55999</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="AI14" s="9">
         <f t="shared" si="12"/>
-        <v>25001</v>
+        <v>25002</v>
       </c>
       <c r="AJ14" s="8">
-        <v>37051</v>
+        <v>37052</v>
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="13"/>
-        <v>0.66163681494312399</v>
+        <v>0.66165467240486442</v>
       </c>
       <c r="AL14" s="5">
         <v>53588</v>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="AN14" s="9">
         <f t="shared" si="14"/>
-        <v>24303</v>
+        <v>24304</v>
       </c>
       <c r="AO14" s="8">
-        <v>37518</v>
+        <v>37519</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="15"/>
-        <v>0.70011942972307228</v>
+        <v>0.70013809061730237</v>
       </c>
       <c r="AQ14" s="22">
         <v>140248</v>
@@ -2094,14 +2094,14 @@
       </c>
       <c r="AS14" s="9">
         <f t="shared" si="16"/>
-        <v>35442</v>
+        <v>35447</v>
       </c>
       <c r="AT14" s="8">
-        <v>125136</v>
+        <v>125141</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="17"/>
-        <v>0.89224801779704521</v>
+        <v>0.8922836689293252</v>
       </c>
       <c r="AV14" s="22">
         <v>71286</v>
@@ -2111,14 +2111,14 @@
       </c>
       <c r="AX14" s="9">
         <f t="shared" si="18"/>
-        <v>35681</v>
+        <v>35684</v>
       </c>
       <c r="AY14" s="9">
-        <v>59688</v>
+        <v>59691</v>
       </c>
       <c r="AZ14" s="10">
         <f t="shared" si="19"/>
-        <v>0.83730325730157396</v>
+        <v>0.83734534130123728</v>
       </c>
       <c r="BA14" s="22">
         <v>69175</v>
@@ -2128,14 +2128,14 @@
       </c>
       <c r="BC14" s="9">
         <f t="shared" si="20"/>
-        <v>34354</v>
+        <v>34357</v>
       </c>
       <c r="BD14" s="8">
-        <v>61431</v>
+        <v>61434</v>
       </c>
       <c r="BE14" s="10">
         <f t="shared" si="21"/>
-        <v>0.88805204192265996</v>
+        <v>0.88809541019154314</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="BH14" s="9">
         <f t="shared" si="22"/>
-        <v>70023</v>
+        <v>70025</v>
       </c>
       <c r="BI14" s="6">
-        <v>129531</v>
+        <v>129533</v>
       </c>
       <c r="BJ14" s="10">
         <f t="shared" si="23"/>
-        <v>0.93411554299148314</v>
+        <v>0.93412996603373555</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="AS15" s="9">
         <f t="shared" si="16"/>
-        <v>68299</v>
+        <v>68300</v>
       </c>
       <c r="AT15" s="8">
-        <v>412863</v>
+        <v>412864</v>
       </c>
       <c r="AU15" s="10">
         <f t="shared" si="17"/>
-        <v>0.90891338901633068</v>
+        <v>0.90891559050541781</v>
       </c>
       <c r="AV15" s="22">
         <v>236575</v>
@@ -2323,14 +2323,14 @@
       </c>
       <c r="AX15" s="9">
         <f t="shared" si="18"/>
-        <v>94718</v>
+        <v>94719</v>
       </c>
       <c r="AY15" s="9">
-        <v>201345</v>
+        <v>201346</v>
       </c>
       <c r="AZ15" s="10">
         <f t="shared" si="19"/>
-        <v>0.85108316601500578</v>
+        <v>0.85108739300433267</v>
       </c>
       <c r="BA15" s="22">
         <v>231251</v>
@@ -2340,14 +2340,14 @@
       </c>
       <c r="BC15" s="9">
         <f t="shared" si="20"/>
-        <v>83874</v>
+        <v>83875</v>
       </c>
       <c r="BD15" s="8">
-        <v>205732</v>
+        <v>205733</v>
       </c>
       <c r="BE15" s="10">
         <f t="shared" si="21"/>
-        <v>0.88964804476521187</v>
+        <v>0.88965236907083645</v>
       </c>
       <c r="BF15" s="9">
         <v>438177</v>
@@ -2416,14 +2416,14 @@
       </c>
       <c r="O16" s="9">
         <f t="shared" si="4"/>
-        <v>326403</v>
+        <v>326404</v>
       </c>
       <c r="P16" s="8">
-        <v>630728</v>
+        <v>630729</v>
       </c>
       <c r="Q16" s="10">
         <f t="shared" si="5"/>
-        <v>0.85729353558418964</v>
+        <v>0.85729489479693366</v>
       </c>
       <c r="R16" s="5">
         <v>377107</v>
@@ -2467,14 +2467,14 @@
       </c>
       <c r="AD16" s="9">
         <f t="shared" si="10"/>
-        <v>218536</v>
+        <v>218537</v>
       </c>
       <c r="AE16" s="8">
-        <v>649884</v>
+        <v>649885</v>
       </c>
       <c r="AF16" s="10">
         <f t="shared" si="11"/>
-        <v>0.85044204707840643</v>
+        <v>0.85044335568432239</v>
       </c>
       <c r="AG16" s="5">
         <v>333237</v>
@@ -2518,14 +2518,14 @@
       </c>
       <c r="AS16" s="9">
         <f t="shared" si="16"/>
-        <v>112000</v>
+        <v>112002</v>
       </c>
       <c r="AT16" s="8">
-        <v>671256</v>
+        <v>671258</v>
       </c>
       <c r="AU16" s="10">
         <f t="shared" si="17"/>
-        <v>0.8748046775730105</v>
+        <v>0.87480728404409624</v>
       </c>
       <c r="AV16" s="22">
         <v>376806</v>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="AX16" s="9">
         <f t="shared" si="18"/>
-        <v>148958</v>
+        <v>148959</v>
       </c>
       <c r="AY16" s="9">
-        <v>307753</v>
+        <v>307754</v>
       </c>
       <c r="AZ16" s="10">
         <f t="shared" si="19"/>
-        <v>0.81674124085072952</v>
+        <v>0.81674389473628339</v>
       </c>
       <c r="BA16" s="22">
         <v>362361</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="BH16" s="9">
         <f t="shared" si="22"/>
-        <v>223696</v>
+        <v>223697</v>
       </c>
       <c r="BI16" s="6">
-        <v>675486</v>
+        <v>675487</v>
       </c>
       <c r="BJ16" s="10">
         <f t="shared" si="23"/>
-        <v>0.94157381994170619</v>
+        <v>0.94157521386226117</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2594,14 +2594,14 @@
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>33426</v>
+        <v>33427</v>
       </c>
       <c r="F17" s="8">
-        <v>138327</v>
+        <v>138328</v>
       </c>
       <c r="G17" s="10">
         <f t="shared" si="1"/>
-        <v>0.25132359727758657</v>
+        <v>0.25132541415785781</v>
       </c>
       <c r="H17" s="5">
         <v>502451</v>
@@ -2611,14 +2611,14 @@
       </c>
       <c r="J17" s="9">
         <f t="shared" si="2"/>
-        <v>39847</v>
+        <v>39848</v>
       </c>
       <c r="K17" s="8">
-        <v>138720</v>
+        <v>138721</v>
       </c>
       <c r="L17" s="10">
         <f t="shared" si="3"/>
-        <v>0.27608662337222933</v>
+        <v>0.27608861361605408</v>
       </c>
       <c r="M17" s="5">
         <v>556868</v>
@@ -2628,14 +2628,14 @@
       </c>
       <c r="O17" s="9">
         <f t="shared" si="4"/>
-        <v>259034</v>
+        <v>259037</v>
       </c>
       <c r="P17" s="8">
-        <v>514381</v>
+        <v>514384</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" si="5"/>
-        <v>0.92370364251492276</v>
+        <v>0.92370902978802871</v>
       </c>
       <c r="R17" s="5">
         <v>233458</v>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="T17" s="9">
         <f t="shared" si="6"/>
-        <v>96612</v>
+        <v>96614</v>
       </c>
       <c r="U17" s="8">
-        <v>141767</v>
+        <v>141769</v>
       </c>
       <c r="V17" s="10">
         <f t="shared" si="7"/>
-        <v>0.60724841299077348</v>
+        <v>0.60725697984219862</v>
       </c>
       <c r="W17" s="5">
         <v>221561</v>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="Y17" s="9">
         <f t="shared" si="8"/>
-        <v>86587</v>
+        <v>86590</v>
       </c>
       <c r="Z17" s="8">
-        <v>142728</v>
+        <v>142731</v>
       </c>
       <c r="AA17" s="10">
         <f t="shared" si="9"/>
-        <v>0.64419279566349674</v>
+        <v>0.644206335952627</v>
       </c>
       <c r="AB17" s="5">
         <v>582052</v>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="AD17" s="9">
         <f t="shared" si="10"/>
-        <v>196958</v>
+        <v>196960</v>
       </c>
       <c r="AE17" s="8">
-        <v>535867</v>
+        <v>535869</v>
       </c>
       <c r="AF17" s="10">
         <f t="shared" si="11"/>
-        <v>0.9206514194608042</v>
+        <v>0.92065485557991378</v>
       </c>
       <c r="AG17" s="5">
         <v>198905</v>
@@ -2696,14 +2696,14 @@
       </c>
       <c r="AI17" s="9">
         <f t="shared" si="12"/>
-        <v>84781</v>
+        <v>84783</v>
       </c>
       <c r="AJ17" s="8">
-        <v>144565</v>
+        <v>144567</v>
       </c>
       <c r="AK17" s="10">
         <f t="shared" si="13"/>
-        <v>0.72680425328674492</v>
+        <v>0.72681430833815142</v>
       </c>
       <c r="AL17" s="5">
         <v>191155</v>
@@ -2713,14 +2713,14 @@
       </c>
       <c r="AN17" s="9">
         <f t="shared" si="14"/>
-        <v>82769</v>
+        <v>82771</v>
       </c>
       <c r="AO17" s="8">
-        <v>146001</v>
+        <v>146003</v>
       </c>
       <c r="AP17" s="10">
         <f t="shared" si="15"/>
-        <v>0.76378331720331671</v>
+        <v>0.7637937799168214</v>
       </c>
       <c r="AQ17" s="22">
         <v>594970</v>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="AS17" s="9">
         <f t="shared" si="16"/>
-        <v>115086</v>
+        <v>115089</v>
       </c>
       <c r="AT17" s="8">
-        <v>556265</v>
+        <v>556268</v>
       </c>
       <c r="AU17" s="10">
         <f t="shared" si="17"/>
-        <v>0.93494629981343602</v>
+        <v>0.93495134208447483</v>
       </c>
       <c r="AV17" s="22">
         <v>254447</v>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="AX17" s="9">
         <f t="shared" si="18"/>
-        <v>115494</v>
+        <v>115496</v>
       </c>
       <c r="AY17" s="9">
-        <v>224993</v>
+        <v>224995</v>
       </c>
       <c r="AZ17" s="10">
         <f t="shared" si="19"/>
-        <v>0.88424308402142682</v>
+        <v>0.88425094420449057</v>
       </c>
       <c r="BA17" s="22">
         <v>254024</v>
@@ -2764,14 +2764,14 @@
       </c>
       <c r="BC17" s="9">
         <f t="shared" si="20"/>
-        <v>106333</v>
+        <v>106336</v>
       </c>
       <c r="BD17" s="8">
-        <v>234312</v>
+        <v>234315</v>
       </c>
       <c r="BE17" s="10">
         <f t="shared" si="21"/>
-        <v>0.92240103297326237</v>
+        <v>0.92241284288098757</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="BH17" s="9">
         <f t="shared" si="22"/>
-        <v>261182</v>
+        <v>261185</v>
       </c>
       <c r="BI17" s="6">
-        <v>572590</v>
+        <v>572593</v>
       </c>
       <c r="BJ17" s="10">
         <f t="shared" si="23"/>
-        <v>0.96921675897463677</v>
+        <v>0.9692218370414506</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>117505</v>
+        <v>117508</v>
       </c>
       <c r="F18" s="8">
-        <v>332225</v>
+        <v>332228</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" si="1"/>
-        <v>0.2889204476277607</v>
+        <v>0.28892305658657741</v>
       </c>
       <c r="H18" s="5">
         <v>1037981</v>
@@ -2823,14 +2823,14 @@
       </c>
       <c r="J18" s="9">
         <f t="shared" si="2"/>
-        <v>131831</v>
+        <v>131834</v>
       </c>
       <c r="K18" s="8">
-        <v>332140</v>
+        <v>332143</v>
       </c>
       <c r="L18" s="10">
         <f t="shared" si="3"/>
-        <v>0.31998658934990137</v>
+        <v>0.31998947957621576</v>
       </c>
       <c r="M18" s="5">
         <v>1134575</v>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="O18" s="9">
         <f t="shared" si="4"/>
-        <v>604415</v>
+        <v>604419</v>
       </c>
       <c r="P18" s="8">
-        <v>1000761</v>
+        <v>1000765</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="5"/>
-        <v>0.88205803935394311</v>
+        <v>0.88206156490315757</v>
       </c>
       <c r="R18" s="5">
         <v>560923</v>
@@ -2857,14 +2857,14 @@
       </c>
       <c r="T18" s="9">
         <f t="shared" si="6"/>
-        <v>280948</v>
+        <v>280951</v>
       </c>
       <c r="U18" s="8">
-        <v>340411</v>
+        <v>340414</v>
       </c>
       <c r="V18" s="10">
         <f t="shared" si="7"/>
-        <v>0.60687652315915019</v>
+        <v>0.60688187148681727</v>
       </c>
       <c r="W18" s="5">
         <v>535952</v>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="8"/>
-        <v>262479</v>
+        <v>262482</v>
       </c>
       <c r="Z18" s="8">
-        <v>344132</v>
+        <v>344135</v>
       </c>
       <c r="AA18" s="10">
         <f t="shared" si="9"/>
-        <v>0.64209481446099648</v>
+        <v>0.64210041197719203</v>
       </c>
       <c r="AB18" s="5">
         <v>1210642</v>
@@ -2891,14 +2891,14 @@
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="10"/>
-        <v>486265</v>
+        <v>486270</v>
       </c>
       <c r="AE18" s="8">
-        <v>1048117</v>
+        <v>1048122</v>
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="11"/>
-        <v>0.86575304673057762</v>
+        <v>0.8657571767706721</v>
       </c>
       <c r="AG18" s="5">
         <v>495943</v>
@@ -2908,14 +2908,14 @@
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="12"/>
-        <v>257048</v>
+        <v>257052</v>
       </c>
       <c r="AJ18" s="8">
-        <v>353153</v>
+        <v>353157</v>
       </c>
       <c r="AK18" s="10">
         <f t="shared" si="13"/>
-        <v>0.71208384834547522</v>
+        <v>0.71209191378847969</v>
       </c>
       <c r="AL18" s="5">
         <v>477702</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="AN18" s="9">
         <f t="shared" si="14"/>
-        <v>255793</v>
+        <v>255795</v>
       </c>
       <c r="AO18" s="8">
-        <v>358374</v>
+        <v>358376</v>
       </c>
       <c r="AP18" s="10">
         <f t="shared" si="15"/>
-        <v>0.75020410213899047</v>
+        <v>0.75020828884953383</v>
       </c>
       <c r="AQ18" s="22">
         <v>1231355</v>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="AS18" s="9">
         <f t="shared" si="16"/>
-        <v>296470</v>
+        <v>296475</v>
       </c>
       <c r="AT18" s="8">
-        <v>1092330</v>
+        <v>1092335</v>
       </c>
       <c r="AU18" s="10">
         <f t="shared" si="17"/>
-        <v>0.88709592278424987</v>
+        <v>0.88709998335167362</v>
       </c>
       <c r="AV18" s="22">
         <v>676361</v>
@@ -2959,14 +2959,14 @@
       </c>
       <c r="AX18" s="9">
         <f t="shared" si="18"/>
-        <v>330640</v>
+        <v>330643</v>
       </c>
       <c r="AY18" s="9">
-        <v>573214</v>
+        <v>573217</v>
       </c>
       <c r="AZ18" s="10">
         <f t="shared" si="19"/>
-        <v>0.84749712062049709</v>
+        <v>0.8475015561216569</v>
       </c>
       <c r="BA18" s="22">
         <v>652080</v>
@@ -2976,14 +2976,14 @@
       </c>
       <c r="BC18" s="9">
         <f t="shared" si="20"/>
-        <v>316147</v>
+        <v>316150</v>
       </c>
       <c r="BD18" s="8">
-        <v>587358</v>
+        <v>587361</v>
       </c>
       <c r="BE18" s="10">
         <f t="shared" si="21"/>
-        <v>0.90074530732425473</v>
+        <v>0.90074990798675014</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -2993,14 +2993,14 @@
       </c>
       <c r="BH18" s="9">
         <f t="shared" si="22"/>
-        <v>595077</v>
+        <v>595080</v>
       </c>
       <c r="BI18" s="6">
-        <v>1125700</v>
+        <v>1125703</v>
       </c>
       <c r="BJ18" s="10">
         <f t="shared" si="23"/>
-        <v>0.93568330565433</v>
+        <v>0.93568579925823592</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="T19" s="9">
         <f t="shared" si="6"/>
-        <v>85576</v>
+        <v>85577</v>
       </c>
       <c r="U19" s="8">
-        <v>95494</v>
+        <v>95495</v>
       </c>
       <c r="V19" s="10">
         <f t="shared" si="7"/>
-        <v>0.52352444546780263</v>
+        <v>0.52352992774360496</v>
       </c>
       <c r="W19" s="5">
         <v>174793</v>
@@ -3120,14 +3120,14 @@
       </c>
       <c r="AI19" s="9">
         <f t="shared" si="12"/>
-        <v>81719</v>
+        <v>81720</v>
       </c>
       <c r="AJ19" s="8">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="AK19" s="10">
         <f t="shared" si="13"/>
-        <v>0.60796066810344829</v>
+        <v>0.60796679075235105</v>
       </c>
       <c r="AL19" s="5">
         <v>160483</v>
@@ -3137,14 +3137,14 @@
       </c>
       <c r="AN19" s="9">
         <f t="shared" si="14"/>
-        <v>83154</v>
+        <v>83155</v>
       </c>
       <c r="AO19" s="8">
-        <v>100625</v>
+        <v>100626</v>
       </c>
       <c r="AP19" s="10">
         <f t="shared" si="15"/>
-        <v>0.62701345313833867</v>
+        <v>0.62701968432793509</v>
       </c>
       <c r="AQ19" s="22">
         <v>372999</v>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="AS19" s="9">
         <f t="shared" si="16"/>
-        <v>120091</v>
+        <v>120094</v>
       </c>
       <c r="AT19" s="8">
-        <v>306827</v>
+        <v>306830</v>
       </c>
       <c r="AU19" s="10">
         <f t="shared" si="17"/>
-        <v>0.82259469864530466</v>
+        <v>0.82260274156230984</v>
       </c>
       <c r="AV19" s="22">
         <v>223136</v>
@@ -3171,14 +3171,14 @@
       </c>
       <c r="AX19" s="9">
         <f t="shared" si="18"/>
-        <v>120775</v>
+        <v>120776</v>
       </c>
       <c r="AY19" s="9">
-        <v>165132</v>
+        <v>165133</v>
       </c>
       <c r="AZ19" s="10">
         <f t="shared" si="19"/>
-        <v>0.74005091065538509</v>
+        <v>0.74005539222716188</v>
       </c>
       <c r="BA19" s="22">
         <v>218799</v>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="BC19" s="9">
         <f t="shared" si="20"/>
-        <v>118610</v>
+        <v>118611</v>
       </c>
       <c r="BD19" s="8">
-        <v>171501</v>
+        <v>171502</v>
       </c>
       <c r="BE19" s="10">
         <f t="shared" si="21"/>
-        <v>0.78382899373397497</v>
+        <v>0.78383356413877581</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3205,14 +3205,14 @@
       </c>
       <c r="BH19" s="9">
         <f t="shared" si="22"/>
-        <v>222004</v>
+        <v>222005</v>
       </c>
       <c r="BI19" s="6">
-        <v>323358</v>
+        <v>323359</v>
       </c>
       <c r="BJ19" s="10">
         <f t="shared" si="23"/>
-        <v>0.85826901230504626</v>
+        <v>0.85827166654280229</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="8"/>
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="Z22" s="8">
-        <v>3782</v>
+        <v>3783</v>
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="9"/>
-        <v>0.69153410129822634</v>
+        <v>0.69171695008228196</v>
       </c>
       <c r="AB22" s="5">
         <v>6814</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="10"/>
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="AE22" s="8">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="11"/>
-        <v>0.79189903140592899</v>
+        <v>0.79204578808335779</v>
       </c>
       <c r="AG22" s="5">
         <v>5399</v>
@@ -3756,14 +3756,14 @@
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="12"/>
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="AJ22" s="8">
-        <v>3852</v>
+        <v>3853</v>
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="13"/>
-        <v>0.71346545656603078</v>
+        <v>0.71365067605112054</v>
       </c>
       <c r="AL22" s="5">
         <v>5432</v>
@@ -3773,14 +3773,14 @@
       </c>
       <c r="AN22" s="9">
         <f t="shared" si="14"/>
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="AO22" s="8">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="AP22" s="10">
         <f t="shared" si="15"/>
-        <v>0.72477908689248893</v>
+        <v>0.72496318114874814</v>
       </c>
       <c r="AQ22" s="22">
         <v>7088</v>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="AS22" s="9">
         <f t="shared" si="16"/>
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="AT22" s="8">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="17"/>
-        <v>0.78992663656884876</v>
+        <v>0.79006772009029347</v>
       </c>
       <c r="AV22" s="22">
         <v>5686</v>
@@ -3824,14 +3824,14 @@
       </c>
       <c r="BC22" s="9">
         <f t="shared" si="20"/>
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="BD22" s="8">
-        <v>4474</v>
+        <v>4475</v>
       </c>
       <c r="BE22" s="10">
         <f t="shared" si="21"/>
-        <v>0.79580220562077553</v>
+        <v>0.795980078263963</v>
       </c>
       <c r="BF22" s="9">
         <v>6948</v>
@@ -3841,14 +3841,14 @@
       </c>
       <c r="BH22" s="9">
         <f t="shared" si="22"/>
-        <v>4139</v>
+        <v>4140</v>
       </c>
       <c r="BI22" s="6">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="BJ22" s="10">
         <f t="shared" si="23"/>
-        <v>0.8393782383419689</v>
+        <v>0.83952216465169838</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="AD23" s="9">
         <f t="shared" si="10"/>
-        <v>4208</v>
+        <v>4209</v>
       </c>
       <c r="AE23" s="8">
-        <v>7106</v>
+        <v>7107</v>
       </c>
       <c r="AF23" s="10">
         <f t="shared" si="11"/>
-        <v>0.62801590808661067</v>
+        <v>0.62810428634555904</v>
       </c>
       <c r="AG23" s="5">
         <v>8891</v>
@@ -4002,14 +4002,14 @@
       </c>
       <c r="AS23" s="9">
         <f t="shared" si="16"/>
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="AT23" s="8">
-        <v>7530</v>
+        <v>7531</v>
       </c>
       <c r="AU23" s="10">
         <f t="shared" si="17"/>
-        <v>0.6495298887259553</v>
+        <v>0.64961614767532128</v>
       </c>
       <c r="AV23" s="22">
         <v>9712</v>
@@ -4053,14 +4053,14 @@
       </c>
       <c r="BH23" s="9">
         <f t="shared" si="22"/>
-        <v>5946</v>
+        <v>5948</v>
       </c>
       <c r="BI23" s="6">
-        <v>7829</v>
+        <v>7831</v>
       </c>
       <c r="BJ23" s="10">
         <f t="shared" si="23"/>
-        <v>0.71237488626023659</v>
+        <v>0.71255686988171063</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="O24" s="9">
         <f t="shared" si="4"/>
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="P24" s="8">
-        <v>4481</v>
+        <v>4482</v>
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="5"/>
-        <v>0.71206102018115369</v>
+        <v>0.71221992690290803</v>
       </c>
       <c r="R24" s="5">
         <v>5052</v>
@@ -4163,14 +4163,14 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="10"/>
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="AE24" s="8">
-        <v>4647</v>
+        <v>4648</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="11"/>
-        <v>0.69743358847366055</v>
+        <v>0.69758367101906049</v>
       </c>
       <c r="AG24" s="5">
         <v>5175</v>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="AS24" s="9">
         <f t="shared" si="16"/>
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="AT24" s="8">
-        <v>4995</v>
+        <v>4996</v>
       </c>
       <c r="AU24" s="10">
         <f t="shared" si="17"/>
-        <v>0.73176091415177258</v>
+        <v>0.73190741283328453</v>
       </c>
       <c r="AV24" s="22">
         <v>5390</v>
@@ -4477,14 +4477,14 @@
       </c>
       <c r="BH25" s="9">
         <f t="shared" si="22"/>
-        <v>12931</v>
+        <v>12932</v>
       </c>
       <c r="BI25" s="6">
-        <v>22393</v>
+        <v>22394</v>
       </c>
       <c r="BJ25" s="10">
         <f t="shared" si="23"/>
-        <v>0.87936383271156493</v>
+        <v>0.87940310229727081</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="E26" s="9">
         <f t="shared" si="0"/>
-        <v>3529</v>
+        <v>3531</v>
       </c>
       <c r="F26" s="8">
-        <v>7628</v>
+        <v>7630</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="1"/>
-        <v>0.28728532690569447</v>
+        <v>0.28736065079843326</v>
       </c>
       <c r="H26" s="5">
         <v>23466</v>
@@ -4519,14 +4519,14 @@
       </c>
       <c r="J26" s="9">
         <f t="shared" si="2"/>
-        <v>3889</v>
+        <v>3891</v>
       </c>
       <c r="K26" s="8">
-        <v>7648</v>
+        <v>7650</v>
       </c>
       <c r="L26" s="10">
         <f t="shared" si="3"/>
-        <v>0.32591834995312369</v>
+        <v>0.32600357964714904</v>
       </c>
       <c r="M26" s="5">
         <v>25760</v>
@@ -4536,14 +4536,14 @@
       </c>
       <c r="O26" s="9">
         <f t="shared" si="4"/>
-        <v>10451</v>
+        <v>10456</v>
       </c>
       <c r="P26" s="8">
-        <v>17322</v>
+        <v>17327</v>
       </c>
       <c r="Q26" s="10">
         <f t="shared" si="5"/>
-        <v>0.67243788819875772</v>
+        <v>0.67263198757763976</v>
       </c>
       <c r="R26" s="5">
         <v>16534</v>
@@ -4553,14 +4553,14 @@
       </c>
       <c r="T26" s="9">
         <f t="shared" si="6"/>
-        <v>6353</v>
+        <v>6355</v>
       </c>
       <c r="U26" s="8">
-        <v>7700</v>
+        <v>7702</v>
       </c>
       <c r="V26" s="10">
         <f t="shared" si="7"/>
-        <v>0.46570702794242169</v>
+        <v>0.4658279908068223</v>
       </c>
       <c r="W26" s="5">
         <v>16064</v>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="Y26" s="9">
         <f t="shared" si="8"/>
-        <v>6291</v>
+        <v>6292</v>
       </c>
       <c r="Z26" s="8">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="9"/>
-        <v>0.48350348605577687</v>
+        <v>0.48356573705179284</v>
       </c>
       <c r="AB26" s="5">
         <v>25659</v>
@@ -4587,14 +4587,14 @@
       </c>
       <c r="AD26" s="9">
         <f t="shared" si="10"/>
-        <v>9226</v>
+        <v>9231</v>
       </c>
       <c r="AE26" s="8">
-        <v>17594</v>
+        <v>17599</v>
       </c>
       <c r="AF26" s="10">
         <f t="shared" si="11"/>
-        <v>0.6856853345804591</v>
+        <v>0.68588019798121513</v>
       </c>
       <c r="AG26" s="5">
         <v>15065</v>
@@ -4604,14 +4604,14 @@
       </c>
       <c r="AI26" s="9">
         <f t="shared" si="12"/>
-        <v>6171</v>
+        <v>6172</v>
       </c>
       <c r="AJ26" s="8">
-        <v>7947</v>
+        <v>7948</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="13"/>
-        <v>0.52751410554264855</v>
+        <v>0.52758048456687689</v>
       </c>
       <c r="AL26" s="5">
         <v>14868</v>
@@ -4621,14 +4621,14 @@
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="14"/>
-        <v>6215</v>
+        <v>6217</v>
       </c>
       <c r="AO26" s="8">
-        <v>7984</v>
+        <v>7986</v>
       </c>
       <c r="AP26" s="10">
         <f t="shared" si="15"/>
-        <v>0.53699219800914721</v>
+        <v>0.53712671509281684</v>
       </c>
       <c r="AQ26" s="22">
         <v>26317</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="AS26" s="9">
         <f t="shared" si="16"/>
-        <v>7567</v>
+        <v>7569</v>
       </c>
       <c r="AT26" s="8">
-        <v>18137</v>
+        <v>18139</v>
       </c>
       <c r="AU26" s="10">
         <f t="shared" si="17"/>
-        <v>0.68917429798229279</v>
+        <v>0.68925029448645359</v>
       </c>
       <c r="AV26" s="22">
         <v>16878</v>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="AX26" s="9">
         <f t="shared" si="18"/>
-        <v>7684</v>
+        <v>7687</v>
       </c>
       <c r="AY26" s="9">
-        <v>10305</v>
+        <v>10308</v>
       </c>
       <c r="AZ26" s="10">
         <f t="shared" si="19"/>
-        <v>0.6105581230003555</v>
+        <v>0.61073586917881262</v>
       </c>
       <c r="BA26" s="22">
         <v>16511</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="BC26" s="9">
         <f t="shared" si="20"/>
-        <v>7378</v>
+        <v>7381</v>
       </c>
       <c r="BD26" s="8">
-        <v>10295</v>
+        <v>10298</v>
       </c>
       <c r="BE26" s="10">
         <f t="shared" si="21"/>
-        <v>0.6235237114650839</v>
+        <v>0.62370540851553513</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="BH26" s="9">
         <f t="shared" si="22"/>
-        <v>12736</v>
+        <v>12739</v>
       </c>
       <c r="BI26" s="6">
-        <v>18483</v>
+        <v>18486</v>
       </c>
       <c r="BJ26" s="10">
         <f t="shared" si="23"/>
-        <v>0.72888240397507686</v>
+        <v>0.72900070983516052</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="E27" s="9">
         <f t="shared" si="0"/>
-        <v>27163</v>
+        <v>27165</v>
       </c>
       <c r="F27" s="8">
-        <v>53282</v>
+        <v>53284</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="1"/>
-        <v>0.36645368950267881</v>
+        <v>0.366467444755466</v>
       </c>
       <c r="H27" s="5">
         <v>133004</v>
@@ -4731,14 +4731,14 @@
       </c>
       <c r="J27" s="9">
         <f t="shared" si="2"/>
-        <v>30767</v>
+        <v>30769</v>
       </c>
       <c r="K27" s="8">
-        <v>53265</v>
+        <v>53267</v>
       </c>
       <c r="L27" s="10">
         <f t="shared" si="3"/>
-        <v>0.40047667739316112</v>
+        <v>0.40049171453490123</v>
       </c>
       <c r="M27" s="5">
         <v>146684</v>
@@ -4748,14 +4748,14 @@
       </c>
       <c r="O27" s="9">
         <f t="shared" si="4"/>
-        <v>89635</v>
+        <v>89637</v>
       </c>
       <c r="P27" s="8">
-        <v>121233</v>
+        <v>121235</v>
       </c>
       <c r="Q27" s="10">
         <f t="shared" si="5"/>
-        <v>0.82649096015925394</v>
+        <v>0.8265045949115104</v>
       </c>
       <c r="R27" s="5">
         <v>100364</v>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="T27" s="9">
         <f t="shared" si="6"/>
-        <v>48157</v>
+        <v>48158</v>
       </c>
       <c r="U27" s="8">
-        <v>54588</v>
+        <v>54589</v>
       </c>
       <c r="V27" s="10">
         <f t="shared" si="7"/>
-        <v>0.54390020326013311</v>
+        <v>0.54391016699214856</v>
       </c>
       <c r="W27" s="5">
         <v>96252</v>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="Y27" s="9">
         <f t="shared" si="8"/>
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="Z27" s="8">
-        <v>55299</v>
+        <v>55300</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="9"/>
-        <v>0.57452312679217055</v>
+        <v>0.5745335161866767</v>
       </c>
       <c r="AB27" s="5">
         <v>156081</v>
@@ -4799,14 +4799,14 @@
       </c>
       <c r="AD27" s="9">
         <f t="shared" si="10"/>
-        <v>70860</v>
+        <v>70863</v>
       </c>
       <c r="AE27" s="8">
-        <v>125738</v>
+        <v>125741</v>
       </c>
       <c r="AF27" s="10">
         <f t="shared" si="11"/>
-        <v>0.80559453104477807</v>
+        <v>0.80561375183398365</v>
       </c>
       <c r="AG27" s="5">
         <v>90207</v>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="AI27" s="9">
         <f t="shared" si="12"/>
-        <v>43214</v>
+        <v>43215</v>
       </c>
       <c r="AJ27" s="8">
-        <v>56368</v>
+        <v>56369</v>
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="13"/>
-        <v>0.62487390113849262</v>
+        <v>0.624884986752691</v>
       </c>
       <c r="AL27" s="5">
         <v>89207</v>
@@ -4850,14 +4850,14 @@
       </c>
       <c r="AS27" s="9">
         <f t="shared" si="16"/>
-        <v>52392</v>
+        <v>52394</v>
       </c>
       <c r="AT27" s="8">
-        <v>131370</v>
+        <v>131372</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="17"/>
-        <v>0.81396069295397655</v>
+        <v>0.81397308483481623</v>
       </c>
       <c r="AV27" s="22">
         <v>108391</v>
@@ -4867,14 +4867,14 @@
       </c>
       <c r="AX27" s="9">
         <f t="shared" si="18"/>
-        <v>57659</v>
+        <v>57662</v>
       </c>
       <c r="AY27" s="9">
-        <v>81727</v>
+        <v>81730</v>
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="19"/>
-        <v>0.75400171600963184</v>
+        <v>0.75402939358433818</v>
       </c>
       <c r="BA27" s="22">
         <v>101826</v>
@@ -4884,14 +4884,14 @@
       </c>
       <c r="BC27" s="9">
         <f t="shared" si="20"/>
-        <v>56641</v>
+        <v>56644</v>
       </c>
       <c r="BD27" s="8">
-        <v>83641</v>
+        <v>83644</v>
       </c>
       <c r="BE27" s="10">
         <f t="shared" si="21"/>
-        <v>0.82141103450985009</v>
+        <v>0.82144049653330187</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4901,14 +4901,14 @@
       </c>
       <c r="BH27" s="9">
         <f t="shared" si="22"/>
-        <v>92694</v>
+        <v>92696</v>
       </c>
       <c r="BI27" s="6">
-        <v>135917</v>
+        <v>135919</v>
       </c>
       <c r="BJ27" s="10">
         <f t="shared" si="23"/>
-        <v>0.87546618057210579</v>
+        <v>0.87547906293679267</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="E28" s="9">
         <f t="shared" si="0"/>
-        <v>71299</v>
+        <v>71300</v>
       </c>
       <c r="F28" s="8">
-        <v>190572</v>
+        <v>190573</v>
       </c>
       <c r="G28" s="10">
         <f t="shared" si="1"/>
-        <v>0.31246536306070849</v>
+        <v>0.31246700267913652</v>
       </c>
       <c r="H28" s="5">
         <v>562058</v>
@@ -4943,14 +4943,14 @@
       </c>
       <c r="J28" s="9">
         <f t="shared" si="2"/>
-        <v>80702</v>
+        <v>80703</v>
       </c>
       <c r="K28" s="8">
-        <v>190260</v>
+        <v>190261</v>
       </c>
       <c r="L28" s="10">
         <f t="shared" si="3"/>
-        <v>0.33850599048496777</v>
+        <v>0.33850776966078233</v>
       </c>
       <c r="M28" s="5">
         <v>606073</v>
@@ -4960,14 +4960,14 @@
       </c>
       <c r="O28" s="9">
         <f t="shared" si="4"/>
-        <v>317140</v>
+        <v>317141</v>
       </c>
       <c r="P28" s="8">
-        <v>515639</v>
+        <v>515640</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" si="5"/>
-        <v>0.85078695140684368</v>
+        <v>0.85078860137310197</v>
       </c>
       <c r="R28" s="5">
         <v>322040</v>
@@ -5011,14 +5011,14 @@
       </c>
       <c r="AD28" s="9">
         <f t="shared" si="10"/>
-        <v>237494</v>
+        <v>237495</v>
       </c>
       <c r="AE28" s="8">
-        <v>521364</v>
+        <v>521365</v>
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="11"/>
-        <v>0.84532308196179085</v>
+        <v>0.84532470333012844</v>
       </c>
       <c r="AG28" s="5">
         <v>279354</v>
@@ -5028,14 +5028,14 @@
       </c>
       <c r="AI28" s="9">
         <f t="shared" si="12"/>
-        <v>132098</v>
+        <v>132099</v>
       </c>
       <c r="AJ28" s="8">
-        <v>195001</v>
+        <v>195002</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="13"/>
-        <v>0.69804262691781749</v>
+        <v>0.69804620660523919</v>
       </c>
       <c r="AL28" s="5">
         <v>276143</v>
@@ -5045,14 +5045,14 @@
       </c>
       <c r="AN28" s="9">
         <f t="shared" si="14"/>
-        <v>129669</v>
+        <v>129670</v>
       </c>
       <c r="AO28" s="8">
-        <v>196867</v>
+        <v>196868</v>
       </c>
       <c r="AP28" s="10">
         <f t="shared" si="15"/>
-        <v>0.71291685829443441</v>
+        <v>0.71292047960658067</v>
       </c>
       <c r="AQ28" s="22">
         <v>625592</v>
@@ -5062,14 +5062,14 @@
       </c>
       <c r="AS28" s="9">
         <f t="shared" si="16"/>
-        <v>155363</v>
+        <v>155364</v>
       </c>
       <c r="AT28" s="8">
-        <v>532675</v>
+        <v>532676</v>
       </c>
       <c r="AU28" s="10">
         <f t="shared" si="17"/>
-        <v>0.85147348431565617</v>
+        <v>0.85147508280157036</v>
       </c>
       <c r="AV28" s="22">
         <v>329857</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="18"/>
-        <v>153809</v>
+        <v>153810</v>
       </c>
       <c r="AY28" s="9">
-        <v>254212</v>
+        <v>254213</v>
       </c>
       <c r="AZ28" s="10">
         <f t="shared" si="19"/>
-        <v>0.77067335239209722</v>
+        <v>0.7706763840088281</v>
       </c>
       <c r="BA28" s="22">
         <v>323426</v>
@@ -5096,14 +5096,14 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="20"/>
-        <v>140115</v>
+        <v>140116</v>
       </c>
       <c r="BD28" s="8">
-        <v>257987</v>
+        <v>257988</v>
       </c>
       <c r="BE28" s="10">
         <f t="shared" si="21"/>
-        <v>0.79766932775967303</v>
+        <v>0.79767241965704672</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="BH28" s="9">
         <f t="shared" si="22"/>
-        <v>279113</v>
+        <v>279114</v>
       </c>
       <c r="BI28" s="6">
-        <v>545825</v>
+        <v>545826</v>
       </c>
       <c r="BJ28" s="10">
         <f t="shared" si="23"/>
-        <v>0.88155584734826642</v>
+        <v>0.88155746243707211</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="O29" s="9">
         <f t="shared" si="4"/>
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="P29" s="8">
-        <v>129719</v>
+        <v>129720</v>
       </c>
       <c r="Q29" s="10">
         <f t="shared" si="5"/>
-        <v>0.89723123318370146</v>
+        <v>0.89723814991319506</v>
       </c>
       <c r="R29" s="5">
         <v>86442</v>
@@ -5223,14 +5223,14 @@
       </c>
       <c r="AD29" s="9">
         <f t="shared" si="10"/>
-        <v>61929</v>
+        <v>61931</v>
       </c>
       <c r="AE29" s="8">
-        <v>133921</v>
+        <v>133923</v>
       </c>
       <c r="AF29" s="10">
         <f t="shared" si="11"/>
-        <v>0.87303532663611416</v>
+        <v>0.87304836470074387</v>
       </c>
       <c r="AG29" s="5">
         <v>79643</v>
@@ -5274,14 +5274,14 @@
       </c>
       <c r="AS29" s="9">
         <f t="shared" si="16"/>
-        <v>41581</v>
+        <v>41582</v>
       </c>
       <c r="AT29" s="8">
-        <v>138706</v>
+        <v>138707</v>
       </c>
       <c r="AU29" s="10">
         <f t="shared" si="17"/>
-        <v>0.89187955324361345</v>
+        <v>0.8918859832434205</v>
       </c>
       <c r="AV29" s="22">
         <v>96040</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="AX29" s="9">
         <f t="shared" si="18"/>
-        <v>51819</v>
+        <v>51820</v>
       </c>
       <c r="AY29" s="9">
-        <v>83591</v>
+        <v>83592</v>
       </c>
       <c r="AZ29" s="10">
         <f t="shared" si="19"/>
-        <v>0.87037692628071639</v>
+        <v>0.87038733860891293</v>
       </c>
       <c r="BA29" s="22">
         <v>92820</v>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="BC29" s="9">
         <f t="shared" si="20"/>
-        <v>48853</v>
+        <v>48854</v>
       </c>
       <c r="BD29" s="8">
-        <v>85033</v>
+        <v>85034</v>
       </c>
       <c r="BE29" s="10">
         <f t="shared" si="21"/>
-        <v>0.91610644257703078</v>
+        <v>0.91611721611721608</v>
       </c>
       <c r="BF29" s="9">
         <v>153057</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="BH29" s="9">
         <f t="shared" si="22"/>
-        <v>83902</v>
+        <v>83903</v>
       </c>
       <c r="BI29" s="6">
-        <v>143674</v>
+        <v>143675</v>
       </c>
       <c r="BJ29" s="10">
         <f t="shared" si="23"/>
-        <v>0.93869604134407447</v>
+        <v>0.93870257485773279</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5384,14 +5384,14 @@
       </c>
       <c r="O30" s="9">
         <f t="shared" si="4"/>
-        <v>132040</v>
+        <v>132041</v>
       </c>
       <c r="P30" s="8">
-        <v>197269</v>
+        <v>197270</v>
       </c>
       <c r="Q30" s="10">
         <f t="shared" si="5"/>
-        <v>0.86812388882043334</v>
+        <v>0.86812828953158827</v>
       </c>
       <c r="R30" s="5">
         <v>127114</v>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="AD30" s="9">
         <f t="shared" si="10"/>
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="AE30" s="8">
-        <v>203373</v>
+        <v>203374</v>
       </c>
       <c r="AF30" s="10">
         <f t="shared" si="11"/>
-        <v>0.83880720133633047</v>
+        <v>0.83881132581303752</v>
       </c>
       <c r="AG30" s="5">
         <v>117700</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="AS30" s="9">
         <f t="shared" si="16"/>
-        <v>74376</v>
+        <v>74377</v>
       </c>
       <c r="AT30" s="8">
-        <v>212365</v>
+        <v>212366</v>
       </c>
       <c r="AU30" s="10">
         <f t="shared" si="17"/>
-        <v>0.85539645137252529</v>
+        <v>0.85540047932652608</v>
       </c>
       <c r="AV30" s="22">
         <v>136681</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="AX30" s="9">
         <f t="shared" si="18"/>
-        <v>78446</v>
+        <v>78448</v>
       </c>
       <c r="AY30" s="9">
-        <v>110633</v>
+        <v>110635</v>
       </c>
       <c r="AZ30" s="10">
         <f t="shared" si="19"/>
-        <v>0.80942486519706469</v>
+        <v>0.80943949780876645</v>
       </c>
       <c r="BA30" s="22">
         <v>130520</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="BC30" s="9">
         <f t="shared" si="20"/>
-        <v>76628</v>
+        <v>76631</v>
       </c>
       <c r="BD30" s="8">
-        <v>113439</v>
+        <v>113442</v>
       </c>
       <c r="BE30" s="10">
         <f t="shared" si="21"/>
-        <v>0.86913116763714371</v>
+        <v>0.86915415262028806</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="BH30" s="9">
         <f t="shared" si="22"/>
-        <v>141118</v>
+        <v>141121</v>
       </c>
       <c r="BI30" s="6">
-        <v>221811</v>
+        <v>221814</v>
       </c>
       <c r="BJ30" s="10">
         <f t="shared" si="23"/>
-        <v>0.90296645185978253</v>
+        <v>0.9029786645063852</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5647,14 +5647,14 @@
       </c>
       <c r="AD31" s="9">
         <f t="shared" si="10"/>
-        <v>52971</v>
+        <v>52974</v>
       </c>
       <c r="AE31" s="8">
-        <v>101303</v>
+        <v>101306</v>
       </c>
       <c r="AF31" s="10">
         <f t="shared" si="11"/>
-        <v>0.89254530876924021</v>
+        <v>0.89257174072018253</v>
       </c>
       <c r="AG31" s="5">
         <v>58990</v>
@@ -5664,14 +5664,14 @@
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="12"/>
-        <v>31528</v>
+        <v>31529</v>
       </c>
       <c r="AJ31" s="8">
-        <v>43729</v>
+        <v>43730</v>
       </c>
       <c r="AK31" s="10">
         <f t="shared" si="13"/>
-        <v>0.74129513476860487</v>
+        <v>0.74131208679437188</v>
       </c>
       <c r="AL31" s="5">
         <v>57896</v>
@@ -5681,14 +5681,14 @@
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="14"/>
-        <v>30991</v>
+        <v>30992</v>
       </c>
       <c r="AO31" s="8">
-        <v>44043</v>
+        <v>44044</v>
       </c>
       <c r="AP31" s="10">
         <f t="shared" si="15"/>
-        <v>0.76072612961171759</v>
+        <v>0.76074340196213897</v>
       </c>
       <c r="AQ31" s="22">
         <v>115872</v>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="AS31" s="9">
         <f t="shared" si="16"/>
-        <v>37969</v>
+        <v>37974</v>
       </c>
       <c r="AT31" s="8">
-        <v>104664</v>
+        <v>104669</v>
       </c>
       <c r="AU31" s="10">
         <f t="shared" si="17"/>
-        <v>0.90327257663628835</v>
+        <v>0.9033157276995305</v>
       </c>
       <c r="AV31" s="22">
         <v>66185</v>
@@ -5715,14 +5715,14 @@
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="18"/>
-        <v>37461</v>
+        <v>37464</v>
       </c>
       <c r="AY31" s="9">
-        <v>57183</v>
+        <v>57186</v>
       </c>
       <c r="AZ31" s="10">
         <f t="shared" si="19"/>
-        <v>0.86398730830248549</v>
+        <v>0.86403263579360878</v>
       </c>
       <c r="BA31" s="22">
         <v>65739</v>
@@ -5749,14 +5749,14 @@
       </c>
       <c r="BH31" s="9">
         <f t="shared" si="22"/>
-        <v>76442</v>
+        <v>76445</v>
       </c>
       <c r="BI31" s="6">
-        <v>109222</v>
+        <v>109225</v>
       </c>
       <c r="BJ31" s="10">
         <f t="shared" si="23"/>
-        <v>0.93905133650299633</v>
+        <v>0.93907712942026123</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="O32" s="9">
         <f t="shared" si="4"/>
-        <v>199316</v>
+        <v>199318</v>
       </c>
       <c r="P32" s="8">
-        <v>329570</v>
+        <v>329572</v>
       </c>
       <c r="Q32" s="10">
         <f t="shared" si="5"/>
-        <v>0.93332200557891909</v>
+        <v>0.93332766945612622</v>
       </c>
       <c r="R32" s="5">
         <v>166950</v>
@@ -5859,14 +5859,14 @@
       </c>
       <c r="AD32" s="9">
         <f t="shared" si="10"/>
-        <v>160708</v>
+        <v>160711</v>
       </c>
       <c r="AE32" s="8">
-        <v>338751</v>
+        <v>338754</v>
       </c>
       <c r="AF32" s="10">
         <f t="shared" si="11"/>
-        <v>0.90496251930135763</v>
+        <v>0.90497053370591407</v>
       </c>
       <c r="AG32" s="5">
         <v>155463</v>
@@ -5876,14 +5876,14 @@
       </c>
       <c r="AI32" s="9">
         <f t="shared" si="12"/>
-        <v>83585</v>
+        <v>83586</v>
       </c>
       <c r="AJ32" s="8">
-        <v>117367</v>
+        <v>117368</v>
       </c>
       <c r="AK32" s="10">
         <f t="shared" si="13"/>
-        <v>0.75495133890379063</v>
+        <v>0.75495777130249642</v>
       </c>
       <c r="AL32" s="5">
         <v>151258</v>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="AN32" s="9">
         <f t="shared" si="14"/>
-        <v>82982</v>
+        <v>82983</v>
       </c>
       <c r="AO32" s="8">
-        <v>118310</v>
+        <v>118311</v>
       </c>
       <c r="AP32" s="10">
         <f t="shared" si="15"/>
-        <v>0.7821735048724695</v>
+        <v>0.78218011609303306</v>
       </c>
       <c r="AQ32" s="22">
         <v>378853</v>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="AS32" s="9">
         <f t="shared" si="16"/>
-        <v>111948</v>
+        <v>111951</v>
       </c>
       <c r="AT32" s="8">
-        <v>348812</v>
+        <v>348815</v>
       </c>
       <c r="AU32" s="10">
         <f t="shared" si="17"/>
-        <v>0.92070539232895077</v>
+        <v>0.92071331096757847</v>
       </c>
       <c r="AV32" s="22">
         <v>171744</v>
@@ -5927,14 +5927,14 @@
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="18"/>
-        <v>96177</v>
+        <v>96180</v>
       </c>
       <c r="AY32" s="9">
-        <v>152312</v>
+        <v>152315</v>
       </c>
       <c r="AZ32" s="10">
         <f t="shared" si="19"/>
-        <v>0.88685485373579276</v>
+        <v>0.88687232159493201</v>
       </c>
       <c r="BA32" s="22">
         <v>169380</v>
@@ -5944,14 +5944,14 @@
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="20"/>
-        <v>93107</v>
+        <v>93110</v>
       </c>
       <c r="BD32" s="8">
-        <v>156569</v>
+        <v>156572</v>
       </c>
       <c r="BE32" s="10">
         <f t="shared" si="21"/>
-        <v>0.92436533238871177</v>
+        <v>0.92438304404298033</v>
       </c>
       <c r="BF32" s="9">
         <v>378386</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="BH32" s="9">
         <f t="shared" si="22"/>
-        <v>248545</v>
+        <v>248550</v>
       </c>
       <c r="BI32" s="6">
-        <v>358223</v>
+        <v>358228</v>
       </c>
       <c r="BJ32" s="10">
         <f t="shared" si="23"/>
-        <v>0.94671314477808377</v>
+        <v>0.9467263587976299</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.3">
@@ -5986,14 +5986,14 @@
       </c>
       <c r="E33" s="9">
         <f t="shared" si="0"/>
-        <v>57422</v>
+        <v>57426</v>
       </c>
       <c r="F33" s="8">
-        <v>294980</v>
+        <v>294984</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
-        <v>0.33094327472061447</v>
+        <v>0.33094776239130019</v>
       </c>
       <c r="H33" s="5">
         <v>840037</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="J33" s="9">
         <f t="shared" si="2"/>
-        <v>65408</v>
+        <v>65412</v>
       </c>
       <c r="K33" s="8">
-        <v>295279</v>
+        <v>295283</v>
       </c>
       <c r="L33" s="10">
         <f t="shared" si="3"/>
-        <v>0.35150713599520023</v>
+        <v>0.35151189769022079</v>
       </c>
       <c r="M33" s="5">
         <v>888717</v>
@@ -6020,14 +6020,14 @@
       </c>
       <c r="O33" s="9">
         <f t="shared" si="4"/>
-        <v>331372</v>
+        <v>331377</v>
       </c>
       <c r="P33" s="8">
-        <v>837846</v>
+        <v>837851</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="5"/>
-        <v>0.94275905603246024</v>
+        <v>0.94276468212040498</v>
       </c>
       <c r="R33" s="5">
         <v>410545</v>
@@ -6037,14 +6037,14 @@
       </c>
       <c r="T33" s="9">
         <f t="shared" si="6"/>
-        <v>191552</v>
+        <v>191556</v>
       </c>
       <c r="U33" s="8">
-        <v>299408</v>
+        <v>299412</v>
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>0.72929398726083616</v>
+        <v>0.72930373040714169</v>
       </c>
       <c r="W33" s="5">
         <v>395753</v>
@@ -6054,14 +6054,14 @@
       </c>
       <c r="Y33" s="9">
         <f t="shared" si="8"/>
-        <v>163291</v>
+        <v>163298</v>
       </c>
       <c r="Z33" s="8">
-        <v>301322</v>
+        <v>301329</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="9"/>
-        <v>0.76138904821947018</v>
+        <v>0.761406736019689</v>
       </c>
       <c r="AB33" s="5">
         <v>919225</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AD33" s="9">
         <f t="shared" si="10"/>
-        <v>217535</v>
+        <v>217537</v>
       </c>
       <c r="AE33" s="8">
-        <v>863406</v>
+        <v>863408</v>
       </c>
       <c r="AF33" s="10">
         <f t="shared" si="11"/>
-        <v>0.93927602056079851</v>
+        <v>0.93927819630667142</v>
       </c>
       <c r="AG33" s="5">
         <v>374721</v>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="12"/>
-        <v>140259</v>
+        <v>140264</v>
       </c>
       <c r="AJ33" s="8">
-        <v>305411</v>
+        <v>305416</v>
       </c>
       <c r="AK33" s="10">
         <f t="shared" si="13"/>
-        <v>0.81503571990894563</v>
+        <v>0.81504906316966486</v>
       </c>
       <c r="AL33" s="5">
         <v>367134</v>
@@ -6105,14 +6105,14 @@
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="14"/>
-        <v>142097</v>
+        <v>142101</v>
       </c>
       <c r="AO33" s="8">
-        <v>307678</v>
+        <v>307682</v>
       </c>
       <c r="AP33" s="10">
         <f t="shared" si="15"/>
-        <v>0.83805368067245201</v>
+        <v>0.83806457587692773</v>
       </c>
       <c r="AQ33" s="22">
         <v>933808</v>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="18"/>
-        <v>148156</v>
+        <v>148158</v>
       </c>
       <c r="AY33" s="9">
-        <v>435397</v>
+        <v>435399</v>
       </c>
       <c r="AZ33" s="10">
         <f t="shared" si="19"/>
-        <v>0.92400171474168524</v>
+        <v>0.92400595915179706</v>
       </c>
       <c r="BA33" s="22">
         <v>469534</v>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="BC33" s="9">
         <f t="shared" si="20"/>
-        <v>133518</v>
+        <v>133521</v>
       </c>
       <c r="BD33" s="8">
-        <v>447373</v>
+        <v>447376</v>
       </c>
       <c r="BE33" s="10">
         <f t="shared" si="21"/>
-        <v>0.95280213999412178</v>
+        <v>0.9528085293077817</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="BH33" s="9">
         <f t="shared" si="22"/>
-        <v>270379</v>
+        <v>270381</v>
       </c>
       <c r="BI33" s="6">
-        <v>916122</v>
+        <v>916124</v>
       </c>
       <c r="BJ33" s="10">
         <f t="shared" si="23"/>
-        <v>0.97881510764463908</v>
+        <v>0.97881724451092478</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
@@ -6605,14 +6605,14 @@
       </c>
       <c r="E36" s="9">
         <f t="shared" si="0"/>
-        <v>160273</v>
+        <v>160276</v>
       </c>
       <c r="F36" s="8">
-        <v>404023</v>
+        <v>404026</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="1"/>
-        <v>0.29323755752826425</v>
+        <v>0.29323973491091965</v>
       </c>
       <c r="H36" s="5">
         <v>1292614</v>
@@ -6622,14 +6622,14 @@
       </c>
       <c r="J36" s="9">
         <f t="shared" si="2"/>
-        <v>174091</v>
+        <v>174095</v>
       </c>
       <c r="K36" s="8">
-        <v>404223</v>
+        <v>404227</v>
       </c>
       <c r="L36" s="10">
         <f t="shared" si="3"/>
-        <v>0.31271748565310292</v>
+        <v>0.31272058015772691</v>
       </c>
       <c r="M36" s="5">
         <v>1376699</v>
@@ -6639,14 +6639,14 @@
       </c>
       <c r="O36" s="9">
         <f t="shared" si="4"/>
-        <v>743410</v>
+        <v>743415</v>
       </c>
       <c r="P36" s="8">
-        <v>1226744</v>
+        <v>1226749</v>
       </c>
       <c r="Q36" s="10">
         <f t="shared" si="5"/>
-        <v>0.89107640813278721</v>
+        <v>0.89108004000874552</v>
       </c>
       <c r="R36" s="5">
         <v>745641</v>
@@ -6656,14 +6656,14 @@
       </c>
       <c r="T36" s="9">
         <f t="shared" si="6"/>
-        <v>301890</v>
+        <v>301893</v>
       </c>
       <c r="U36" s="8">
-        <v>409708</v>
+        <v>409711</v>
       </c>
       <c r="V36" s="10">
         <f t="shared" si="7"/>
-        <v>0.54947085795979567</v>
+        <v>0.54947488134370293</v>
       </c>
       <c r="W36" s="5">
         <v>686690</v>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="Y36" s="9">
         <f t="shared" si="8"/>
-        <v>276528</v>
+        <v>276529</v>
       </c>
       <c r="Z36" s="8">
-        <v>412189</v>
+        <v>412190</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" si="9"/>
-        <v>0.60025484570912635</v>
+        <v>0.60025630197032143</v>
       </c>
       <c r="AB36" s="5">
         <v>1408098</v>
@@ -6690,14 +6690,14 @@
       </c>
       <c r="AD36" s="9">
         <f t="shared" si="10"/>
-        <v>511512</v>
+        <v>511521</v>
       </c>
       <c r="AE36" s="8">
-        <v>1248578</v>
+        <v>1248587</v>
       </c>
       <c r="AF36" s="10">
         <f t="shared" si="11"/>
-        <v>0.88671243052685256</v>
+        <v>0.88671882212743713</v>
       </c>
       <c r="AG36" s="5">
         <v>587071</v>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="AI36" s="9">
         <f t="shared" si="12"/>
-        <v>248206</v>
+        <v>248207</v>
       </c>
       <c r="AJ36" s="8">
-        <v>417513</v>
+        <v>417514</v>
       </c>
       <c r="AK36" s="10">
         <f t="shared" si="13"/>
-        <v>0.71117973805553336</v>
+        <v>0.71118144142701645</v>
       </c>
       <c r="AL36" s="5">
         <v>562582</v>
@@ -6724,14 +6724,14 @@
       </c>
       <c r="AN36" s="9">
         <f t="shared" si="14"/>
-        <v>238185</v>
+        <v>238186</v>
       </c>
       <c r="AO36" s="8">
-        <v>421204</v>
+        <v>421205</v>
       </c>
       <c r="AP36" s="10">
         <f t="shared" si="15"/>
-        <v>0.74869796758516982</v>
+        <v>0.74869974510382487</v>
       </c>
       <c r="AQ36" s="22">
         <v>1406326</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="AS36" s="9">
         <f t="shared" si="16"/>
-        <v>335774</v>
+        <v>335784</v>
       </c>
       <c r="AT36" s="8">
-        <v>1284262</v>
+        <v>1284272</v>
       </c>
       <c r="AU36" s="10">
         <f t="shared" si="17"/>
-        <v>0.91320362419524348</v>
+        <v>0.91321073492205929</v>
       </c>
       <c r="AV36" s="22">
         <v>685313</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="AX36" s="9">
         <f t="shared" si="18"/>
-        <v>333905</v>
+        <v>333914</v>
       </c>
       <c r="AY36" s="9">
-        <v>603413</v>
+        <v>603422</v>
       </c>
       <c r="AZ36" s="10">
         <f t="shared" si="19"/>
-        <v>0.88049256325211989</v>
+        <v>0.88050569593747674</v>
       </c>
       <c r="BA36" s="22">
         <v>667446</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="BC36" s="9">
         <f t="shared" si="20"/>
-        <v>306863</v>
+        <v>306872</v>
       </c>
       <c r="BD36" s="8">
-        <v>617053</v>
+        <v>617062</v>
       </c>
       <c r="BE36" s="10">
         <f t="shared" si="21"/>
-        <v>0.92449876094845129</v>
+        <v>0.92451224518537833</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="BH36" s="9">
         <f t="shared" si="22"/>
-        <v>656322</v>
+        <v>656332</v>
       </c>
       <c r="BI36" s="6">
-        <v>1309787</v>
+        <v>1309797</v>
       </c>
       <c r="BJ36" s="10">
         <f t="shared" si="23"/>
-        <v>0.96025932684405269</v>
+        <v>0.96026665825997637</v>
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="E37" s="9">
         <f t="shared" si="0"/>
-        <v>126105</v>
+        <v>126107</v>
       </c>
       <c r="F37" s="8">
-        <v>409808</v>
+        <v>409810</v>
       </c>
       <c r="G37" s="10">
         <f t="shared" si="1"/>
-        <v>0.55925412404336383</v>
+        <v>0.55925685339039488</v>
       </c>
       <c r="H37" s="5">
         <v>674591</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="J37" s="9">
         <f t="shared" si="2"/>
-        <v>147517</v>
+        <v>147520</v>
       </c>
       <c r="K37" s="8">
-        <v>413315</v>
+        <v>413318</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" si="3"/>
-        <v>0.61268976313054868</v>
+        <v>0.61269421026963</v>
       </c>
       <c r="M37" s="5">
         <v>737436</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="O37" s="9">
         <f t="shared" si="4"/>
-        <v>346117</v>
+        <v>346123</v>
       </c>
       <c r="P37" s="8">
-        <v>645268</v>
+        <v>645274</v>
       </c>
       <c r="Q37" s="10">
         <f t="shared" si="5"/>
-        <v>0.87501559457363076</v>
+        <v>0.87502373087291641</v>
       </c>
       <c r="R37" s="5">
         <v>540612</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="T37" s="9">
         <f t="shared" si="6"/>
-        <v>330392</v>
+        <v>330394</v>
       </c>
       <c r="U37" s="8">
-        <v>420085</v>
+        <v>420087</v>
       </c>
       <c r="V37" s="10">
         <f t="shared" si="7"/>
-        <v>0.77705452339200753</v>
+        <v>0.77705822290293225</v>
       </c>
       <c r="W37" s="5">
         <v>536259</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="Y37" s="9">
         <f t="shared" si="8"/>
-        <v>307349</v>
+        <v>307352</v>
       </c>
       <c r="Z37" s="8">
-        <v>423778</v>
+        <v>423781</v>
       </c>
       <c r="AA37" s="10">
         <f t="shared" si="9"/>
-        <v>0.7902487417460593</v>
+        <v>0.79025433605776318</v>
       </c>
       <c r="AB37" s="5">
         <v>768520</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="AD37" s="9">
         <f t="shared" si="10"/>
-        <v>226292</v>
+        <v>226298</v>
       </c>
       <c r="AE37" s="8">
-        <v>661230</v>
+        <v>661236</v>
       </c>
       <c r="AF37" s="10">
         <f t="shared" si="11"/>
-        <v>0.86039400405975119</v>
+        <v>0.86040181127361681</v>
       </c>
       <c r="AG37" s="5">
         <v>524373</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="AI37" s="9">
         <f t="shared" si="12"/>
-        <v>282817</v>
+        <v>282824</v>
       </c>
       <c r="AJ37" s="8">
-        <v>431790</v>
+        <v>431797</v>
       </c>
       <c r="AK37" s="10">
         <f t="shared" si="13"/>
-        <v>0.82344056616187333</v>
+        <v>0.82345391543805646</v>
       </c>
       <c r="AL37" s="5">
         <v>516478</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="AN37" s="9">
         <f t="shared" si="14"/>
-        <v>278004</v>
+        <v>278008</v>
       </c>
       <c r="AO37" s="8">
-        <v>437377</v>
+        <v>437381</v>
       </c>
       <c r="AP37" s="10">
         <f t="shared" si="15"/>
-        <v>0.84684536417814504</v>
+        <v>0.84685310894171684</v>
       </c>
       <c r="AQ37" s="22">
         <v>769503</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="AS37" s="9">
         <f t="shared" si="16"/>
-        <v>145927</v>
+        <v>145938</v>
       </c>
       <c r="AT37" s="8">
-        <v>682734</v>
+        <v>682745</v>
       </c>
       <c r="AU37" s="10">
         <f t="shared" si="17"/>
-        <v>0.88724020569120587</v>
+        <v>0.88725450063222622</v>
       </c>
       <c r="AV37" s="22">
         <v>526610</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="AX37" s="9">
         <f t="shared" si="18"/>
-        <v>255403</v>
+        <v>255407</v>
       </c>
       <c r="AY37" s="9">
-        <v>463258</v>
+        <v>463262</v>
       </c>
       <c r="AZ37" s="10">
         <f t="shared" si="19"/>
-        <v>0.87969844856725088</v>
+        <v>0.87970604432122446</v>
       </c>
       <c r="BA37" s="22">
         <v>525208</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="BC37" s="9">
         <f t="shared" si="20"/>
-        <v>248176</v>
+        <v>248182</v>
       </c>
       <c r="BD37" s="8">
-        <v>471695</v>
+        <v>471701</v>
       </c>
       <c r="BE37" s="10">
         <f t="shared" si="21"/>
-        <v>0.89811084370382777</v>
+        <v>0.89812226774915838</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="BH37" s="9">
         <f t="shared" si="22"/>
-        <v>359931</v>
+        <v>359938</v>
       </c>
       <c r="BI37" s="6">
-        <v>707100</v>
+        <v>707107</v>
       </c>
       <c r="BJ37" s="10">
         <f t="shared" si="23"/>
-        <v>0.92393086786259815</v>
+        <v>0.92394001439926199</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="E40" s="9">
         <f t="shared" si="0"/>
-        <v>58090</v>
+        <v>58094</v>
       </c>
       <c r="F40" s="8">
-        <v>174011</v>
+        <v>174015</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="1"/>
-        <v>0.5736613765684031</v>
+        <v>0.57367456335260802</v>
       </c>
       <c r="H40" s="5">
         <v>287028</v>
@@ -7470,14 +7470,14 @@
       </c>
       <c r="J40" s="9">
         <f t="shared" si="2"/>
-        <v>72969</v>
+        <v>72971</v>
       </c>
       <c r="K40" s="8">
-        <v>174661</v>
+        <v>174663</v>
       </c>
       <c r="L40" s="10">
         <f t="shared" si="3"/>
-        <v>0.60851554552169129</v>
+        <v>0.60852251348300512</v>
       </c>
       <c r="M40" s="5">
         <v>303033</v>
@@ -7487,14 +7487,14 @@
       </c>
       <c r="O40" s="9">
         <f t="shared" si="4"/>
-        <v>166286</v>
+        <v>166290</v>
       </c>
       <c r="P40" s="8">
-        <v>273172</v>
+        <v>273176</v>
       </c>
       <c r="Q40" s="10">
         <f t="shared" si="5"/>
-        <v>0.90145957700976465</v>
+        <v>0.90147277689228567</v>
       </c>
       <c r="R40" s="5">
         <v>226941</v>
@@ -7504,14 +7504,14 @@
       </c>
       <c r="T40" s="9">
         <f t="shared" si="6"/>
-        <v>150778</v>
+        <v>150781</v>
       </c>
       <c r="U40" s="8">
-        <v>177640</v>
+        <v>177643</v>
       </c>
       <c r="V40" s="10">
         <f t="shared" si="7"/>
-        <v>0.78275851432751242</v>
+        <v>0.78277173362239527</v>
       </c>
       <c r="W40" s="5">
         <v>224663</v>
@@ -7521,14 +7521,14 @@
       </c>
       <c r="Y40" s="9">
         <f t="shared" si="8"/>
-        <v>132207</v>
+        <v>132210</v>
       </c>
       <c r="Z40" s="8">
-        <v>179932</v>
+        <v>179935</v>
       </c>
       <c r="AA40" s="10">
         <f t="shared" si="9"/>
-        <v>0.80089734402193513</v>
+        <v>0.80091069735559484</v>
       </c>
       <c r="AB40" s="5">
         <v>313197</v>
@@ -7538,14 +7538,14 @@
       </c>
       <c r="AD40" s="9">
         <f t="shared" si="10"/>
-        <v>87376</v>
+        <v>87379</v>
       </c>
       <c r="AE40" s="8">
-        <v>280662</v>
+        <v>280665</v>
       </c>
       <c r="AF40" s="10">
         <f t="shared" si="11"/>
-        <v>0.89611969463309038</v>
+        <v>0.89612927326890102</v>
       </c>
       <c r="AG40" s="5">
         <v>217708</v>
@@ -7555,14 +7555,14 @@
       </c>
       <c r="AI40" s="9">
         <f t="shared" si="12"/>
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="AJ40" s="8">
-        <v>184516</v>
+        <v>184518</v>
       </c>
       <c r="AK40" s="10">
         <f t="shared" si="13"/>
-        <v>0.8475389053227258</v>
+        <v>0.8475480919396623</v>
       </c>
       <c r="AL40" s="5">
         <v>217966</v>
@@ -7572,14 +7572,14 @@
       </c>
       <c r="AN40" s="9">
         <f t="shared" si="14"/>
-        <v>88626</v>
+        <v>88627</v>
       </c>
       <c r="AO40" s="8">
-        <v>187519</v>
+        <v>187520</v>
       </c>
       <c r="AP40" s="10">
         <f t="shared" si="15"/>
-        <v>0.86031307635135756</v>
+        <v>0.86031766422286049</v>
       </c>
       <c r="AQ40" s="22">
         <v>320883</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="AS40" s="9">
         <f t="shared" si="16"/>
-        <v>54269</v>
+        <v>54274</v>
       </c>
       <c r="AT40" s="8">
-        <v>291081</v>
+        <v>291086</v>
       </c>
       <c r="AU40" s="10">
         <f t="shared" si="17"/>
-        <v>0.90712502687895591</v>
+        <v>0.90714060888236525</v>
       </c>
       <c r="AV40" s="22">
         <v>237287</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="AX40" s="9">
         <f t="shared" si="18"/>
-        <v>104145</v>
+        <v>104147</v>
       </c>
       <c r="AY40" s="9">
-        <v>212775</v>
+        <v>212777</v>
       </c>
       <c r="AZ40" s="10">
         <f t="shared" si="19"/>
-        <v>0.89669893420204227</v>
+        <v>0.89670736281380781</v>
       </c>
       <c r="BA40" s="22">
         <v>231690</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="BC40" s="9">
         <f t="shared" si="20"/>
-        <v>100500</v>
+        <v>100503</v>
       </c>
       <c r="BD40" s="8">
-        <v>215382</v>
+        <v>215385</v>
       </c>
       <c r="BE40" s="10">
         <f t="shared" si="21"/>
-        <v>0.92961284474944972</v>
+        <v>0.92962579308558846</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="BH40" s="9">
         <f t="shared" si="22"/>
-        <v>147488</v>
+        <v>147492</v>
       </c>
       <c r="BI40" s="6">
-        <v>298976</v>
+        <v>298980</v>
       </c>
       <c r="BJ40" s="10">
         <f t="shared" si="23"/>
-        <v>0.95096869821337127</v>
+        <v>0.95098142122388996</v>
       </c>
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="E41" s="9">
         <f t="shared" si="0"/>
-        <v>174780</v>
+        <v>174810</v>
       </c>
       <c r="F41" s="8">
-        <v>589471</v>
+        <v>589501</v>
       </c>
       <c r="G41" s="10">
         <f t="shared" si="1"/>
-        <v>0.67356644411408795</v>
+        <v>0.67360072399100035</v>
       </c>
       <c r="H41" s="5">
         <v>834053</v>
@@ -7682,14 +7682,14 @@
       </c>
       <c r="J41" s="9">
         <f t="shared" si="2"/>
-        <v>212077</v>
+        <v>212103</v>
       </c>
       <c r="K41" s="8">
-        <v>593158</v>
+        <v>593184</v>
       </c>
       <c r="L41" s="10">
         <f t="shared" si="3"/>
-        <v>0.71117542889960228</v>
+        <v>0.71120660197853136</v>
       </c>
       <c r="M41" s="5">
         <v>879453</v>
@@ -7699,14 +7699,14 @@
       </c>
       <c r="O41" s="9">
         <f t="shared" si="4"/>
-        <v>392436</v>
+        <v>392475</v>
       </c>
       <c r="P41" s="8">
-        <v>788520</v>
+        <v>788559</v>
       </c>
       <c r="Q41" s="10">
         <f t="shared" si="5"/>
-        <v>0.89660277467926086</v>
+        <v>0.89664712042599204</v>
       </c>
       <c r="R41" s="5">
         <v>738453</v>
@@ -7716,14 +7716,14 @@
       </c>
       <c r="T41" s="9">
         <f t="shared" si="6"/>
-        <v>486316</v>
+        <v>486342</v>
       </c>
       <c r="U41" s="8">
-        <v>605684</v>
+        <v>605710</v>
       </c>
       <c r="V41" s="10">
         <f t="shared" si="7"/>
-        <v>0.82020656697176397</v>
+        <v>0.82024177571219836</v>
       </c>
       <c r="W41" s="5">
         <v>740008</v>
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Y41" s="9">
         <f t="shared" si="8"/>
-        <v>428204</v>
+        <v>428232</v>
       </c>
       <c r="Z41" s="8">
-        <v>611321</v>
+        <v>611349</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" si="9"/>
-        <v>0.8261005286429336</v>
+        <v>0.82613836607171809</v>
       </c>
       <c r="AB41" s="5">
         <v>928683</v>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="AD41" s="9">
         <f t="shared" si="10"/>
-        <v>220763</v>
+        <v>220802</v>
       </c>
       <c r="AE41" s="8">
-        <v>813281</v>
+        <v>813320</v>
       </c>
       <c r="AF41" s="10">
         <f t="shared" si="11"/>
-        <v>0.87573585389201702</v>
+        <v>0.87577784884616172</v>
       </c>
       <c r="AG41" s="5">
         <v>734303</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="AI41" s="9">
         <f t="shared" si="12"/>
-        <v>376605</v>
+        <v>376630</v>
       </c>
       <c r="AJ41" s="8">
-        <v>623764</v>
+        <v>623789</v>
       </c>
       <c r="AK41" s="10">
         <f t="shared" si="13"/>
-        <v>0.84946404958171218</v>
+        <v>0.84949809547284971</v>
       </c>
       <c r="AL41" s="5">
         <v>728636</v>
@@ -7784,14 +7784,14 @@
       </c>
       <c r="AN41" s="9">
         <f t="shared" si="14"/>
-        <v>357990</v>
+        <v>358020</v>
       </c>
       <c r="AO41" s="8">
-        <v>631411</v>
+        <v>631441</v>
       </c>
       <c r="AP41" s="10">
         <f t="shared" si="15"/>
-        <v>0.86656574750629944</v>
+        <v>0.86660692032784548</v>
       </c>
       <c r="AQ41" s="22">
         <v>923873</v>
@@ -7801,14 +7801,14 @@
       </c>
       <c r="AS41" s="9">
         <f t="shared" si="16"/>
-        <v>140586</v>
+        <v>140622</v>
       </c>
       <c r="AT41" s="8">
-        <v>842193</v>
+        <v>842229</v>
       </c>
       <c r="AU41" s="10">
         <f t="shared" si="17"/>
-        <v>0.91158957995308876</v>
+        <v>0.91162854634782053</v>
       </c>
       <c r="AV41" s="22">
         <v>726271</v>
@@ -7818,14 +7818,14 @@
       </c>
       <c r="AX41" s="9">
         <f t="shared" si="18"/>
-        <v>326001</v>
+        <v>326026</v>
       </c>
       <c r="AY41" s="9">
-        <v>662998</v>
+        <v>663023</v>
       </c>
       <c r="AZ41" s="10">
         <f t="shared" si="19"/>
-        <v>0.91287962757703389</v>
+        <v>0.91291404998960446</v>
       </c>
       <c r="BA41" s="22">
         <v>715104</v>
@@ -7835,14 +7835,14 @@
       </c>
       <c r="BC41" s="9">
         <f t="shared" si="20"/>
-        <v>312348</v>
+        <v>312370</v>
       </c>
       <c r="BD41" s="8">
-        <v>671106</v>
+        <v>671128</v>
       </c>
       <c r="BE41" s="10">
         <f t="shared" si="21"/>
-        <v>0.93847328500469862</v>
+        <v>0.93850404976059432</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7852,14 +7852,14 @@
       </c>
       <c r="BH41" s="9">
         <f t="shared" si="22"/>
-        <v>398032</v>
+        <v>398058</v>
       </c>
       <c r="BI41" s="6">
-        <v>867243</v>
+        <v>867269</v>
       </c>
       <c r="BJ41" s="10">
         <f t="shared" si="23"/>
-        <v>0.95209880609304243</v>
+        <v>0.95212735007547689</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="AX43" s="9">
         <f t="shared" si="18"/>
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="AY43" s="9">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="AZ43" s="10">
         <f t="shared" si="19"/>
-        <v>0.86210191082802545</v>
+        <v>0.86242038216560513</v>
       </c>
       <c r="BA43" s="22">
         <v>3100</v>
@@ -8259,14 +8259,14 @@
       </c>
       <c r="BC43" s="9">
         <f t="shared" si="20"/>
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="BD43" s="8">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="BE43" s="10">
         <f t="shared" si="21"/>
-        <v>0.88193548387096776</v>
+        <v>0.88225806451612898</v>
       </c>
       <c r="BF43" s="9">
         <v>3984</v>
@@ -8276,14 +8276,14 @@
       </c>
       <c r="BH43" s="9">
         <f t="shared" si="22"/>
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="BI43" s="6">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="BJ43" s="10">
         <f t="shared" si="23"/>
-        <v>0.91214859437751006</v>
+        <v>0.91239959839357432</v>
       </c>
     </row>
     <row r="44" spans="1:63" x14ac:dyDescent="0.3">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="E44" s="9">
         <f t="shared" si="0"/>
-        <v>61746</v>
+        <v>61747</v>
       </c>
       <c r="F44" s="8">
-        <v>191700</v>
+        <v>191701</v>
       </c>
       <c r="G44" s="10">
         <f t="shared" si="1"/>
-        <v>0.53712223523544278</v>
+        <v>0.53712503712503712</v>
       </c>
       <c r="H44" s="5">
         <v>334097</v>
@@ -8318,14 +8318,14 @@
       </c>
       <c r="J44" s="9">
         <f t="shared" si="2"/>
-        <v>70948</v>
+        <v>70950</v>
       </c>
       <c r="K44" s="8">
-        <v>192799</v>
+        <v>192801</v>
       </c>
       <c r="L44" s="10">
         <f t="shared" si="3"/>
-        <v>0.57707492135517524</v>
+        <v>0.57708090764059539</v>
       </c>
       <c r="M44" s="5">
         <v>358237</v>
@@ -8335,14 +8335,14 @@
       </c>
       <c r="O44" s="9">
         <f t="shared" si="4"/>
-        <v>149476</v>
+        <v>149479</v>
       </c>
       <c r="P44" s="8">
-        <v>285573</v>
+        <v>285576</v>
       </c>
       <c r="Q44" s="10">
         <f t="shared" si="5"/>
-        <v>0.79716221384167463</v>
+        <v>0.79717058818603326</v>
       </c>
       <c r="R44" s="5">
         <v>284869</v>
@@ -8352,14 +8352,14 @@
       </c>
       <c r="T44" s="9">
         <f t="shared" si="6"/>
-        <v>159515</v>
+        <v>159517</v>
       </c>
       <c r="U44" s="8">
-        <v>196739</v>
+        <v>196741</v>
       </c>
       <c r="V44" s="10">
         <f t="shared" si="7"/>
-        <v>0.69062972805043721</v>
+        <v>0.69063674882138804</v>
       </c>
       <c r="W44" s="5">
         <v>281986</v>
@@ -8369,14 +8369,14 @@
       </c>
       <c r="Y44" s="9">
         <f t="shared" si="8"/>
-        <v>150399</v>
+        <v>150401</v>
       </c>
       <c r="Z44" s="8">
-        <v>198491</v>
+        <v>198493</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" si="9"/>
-        <v>0.70390373990198096</v>
+        <v>0.70391083245267494</v>
       </c>
       <c r="AB44" s="5">
         <v>371659</v>
@@ -8386,14 +8386,14 @@
       </c>
       <c r="AD44" s="9">
         <f t="shared" si="10"/>
-        <v>117182</v>
+        <v>117185</v>
       </c>
       <c r="AE44" s="8">
-        <v>293349</v>
+        <v>293352</v>
       </c>
       <c r="AF44" s="10">
         <f t="shared" si="11"/>
-        <v>0.78929610207206069</v>
+        <v>0.78930417398744546</v>
       </c>
       <c r="AG44" s="5">
         <v>277254</v>
@@ -8403,14 +8403,14 @@
       </c>
       <c r="AI44" s="9">
         <f t="shared" si="12"/>
-        <v>144604</v>
+        <v>144606</v>
       </c>
       <c r="AJ44" s="8">
-        <v>202643</v>
+        <v>202645</v>
       </c>
       <c r="AK44" s="10">
         <f t="shared" si="13"/>
-        <v>0.73089297178760271</v>
+        <v>0.73090018538957058</v>
       </c>
       <c r="AL44" s="5">
         <v>276584</v>
@@ -8420,14 +8420,14 @@
       </c>
       <c r="AN44" s="9">
         <f t="shared" si="14"/>
-        <v>143872</v>
+        <v>143874</v>
       </c>
       <c r="AO44" s="8">
-        <v>205764</v>
+        <v>205766</v>
       </c>
       <c r="AP44" s="10">
         <f t="shared" si="15"/>
-        <v>0.74394758915917047</v>
+        <v>0.74395482023544379</v>
       </c>
       <c r="AQ44" s="22">
         <v>381213</v>
@@ -8437,14 +8437,14 @@
       </c>
       <c r="AS44" s="9">
         <f t="shared" si="16"/>
-        <v>79476</v>
+        <v>79479</v>
       </c>
       <c r="AT44" s="8">
-        <v>306661</v>
+        <v>306664</v>
       </c>
       <c r="AU44" s="10">
         <f t="shared" si="17"/>
-        <v>0.80443479104857385</v>
+        <v>0.80444266066477266</v>
       </c>
       <c r="AV44" s="22">
         <v>286200</v>
@@ -8454,14 +8454,14 @@
       </c>
       <c r="AX44" s="9">
         <f t="shared" si="18"/>
-        <v>140926</v>
+        <v>140928</v>
       </c>
       <c r="AY44" s="9">
-        <v>225302</v>
+        <v>225304</v>
       </c>
       <c r="AZ44" s="10">
         <f t="shared" si="19"/>
-        <v>0.78721872816212435</v>
+        <v>0.78722571628232008</v>
       </c>
       <c r="BA44" s="22">
         <v>282748</v>
@@ -8471,14 +8471,14 @@
       </c>
       <c r="BC44" s="9">
         <f t="shared" si="20"/>
-        <v>139544</v>
+        <v>139545</v>
       </c>
       <c r="BD44" s="8">
-        <v>229343</v>
+        <v>229344</v>
       </c>
       <c r="BE44" s="10">
         <f t="shared" si="21"/>
-        <v>0.81112156407826053</v>
+        <v>0.81112510079646893</v>
       </c>
       <c r="BF44" s="9">
         <v>372165</v>
@@ -8488,14 +8488,14 @@
       </c>
       <c r="BH44" s="9">
         <f t="shared" si="22"/>
-        <v>189931</v>
+        <v>189933</v>
       </c>
       <c r="BI44" s="6">
-        <v>317819</v>
+        <v>317821</v>
       </c>
       <c r="BJ44" s="10">
         <f t="shared" si="23"/>
-        <v>0.85397337202584878</v>
+        <v>0.85397874598632328</v>
       </c>
     </row>
     <row r="45" spans="1:63" x14ac:dyDescent="0.3">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="J45" s="9">
         <f t="shared" si="2"/>
-        <v>59042</v>
+        <v>59043</v>
       </c>
       <c r="K45" s="8">
-        <v>167752</v>
+        <v>167753</v>
       </c>
       <c r="L45" s="10">
         <f t="shared" si="3"/>
-        <v>0.63334428222466366</v>
+        <v>0.63334805770443281</v>
       </c>
       <c r="M45" s="5">
         <v>281786</v>
@@ -8547,14 +8547,14 @@
       </c>
       <c r="O45" s="9">
         <f t="shared" si="4"/>
-        <v>129923</v>
+        <v>129924</v>
       </c>
       <c r="P45" s="8">
-        <v>241336</v>
+        <v>241337</v>
       </c>
       <c r="Q45" s="10">
         <f t="shared" si="5"/>
-        <v>0.85645134960572922</v>
+        <v>0.85645489839807509</v>
       </c>
       <c r="R45" s="5">
         <v>221339</v>
@@ -8564,14 +8564,14 @@
       </c>
       <c r="T45" s="9">
         <f t="shared" si="6"/>
-        <v>140345</v>
+        <v>140346</v>
       </c>
       <c r="U45" s="8">
-        <v>170636</v>
+        <v>170637</v>
       </c>
       <c r="V45" s="10">
         <f t="shared" si="7"/>
-        <v>0.77092604556811051</v>
+        <v>0.770930563524729</v>
       </c>
       <c r="W45" s="5">
         <v>220187</v>
@@ -8581,14 +8581,14 @@
       </c>
       <c r="Y45" s="9">
         <f t="shared" si="8"/>
-        <v>128837</v>
+        <v>128839</v>
       </c>
       <c r="Z45" s="8">
-        <v>171554</v>
+        <v>171556</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" si="9"/>
-        <v>0.77912864973863127</v>
+        <v>0.77913773292701205</v>
       </c>
       <c r="AB45" s="5">
         <v>291802</v>
@@ -8598,14 +8598,14 @@
       </c>
       <c r="AD45" s="9">
         <f t="shared" si="10"/>
-        <v>84798</v>
+        <v>84800</v>
       </c>
       <c r="AE45" s="8">
-        <v>245746</v>
+        <v>245748</v>
       </c>
       <c r="AF45" s="10">
         <f t="shared" si="11"/>
-        <v>0.84216694882146115</v>
+        <v>0.84217380278407961</v>
       </c>
       <c r="AG45" s="5">
         <v>216277</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="BH45" s="9">
         <f t="shared" si="22"/>
-        <v>145219</v>
+        <v>145220</v>
       </c>
       <c r="BI45" s="6">
-        <v>262773</v>
+        <v>262774</v>
       </c>
       <c r="BJ45" s="10">
         <f t="shared" si="23"/>
-        <v>0.90391945071275248</v>
+        <v>0.90392289063789977</v>
       </c>
     </row>
     <row r="46" spans="1:63" x14ac:dyDescent="0.3">
@@ -9135,10 +9135,10 @@
       </c>
     </row>
     <row r="48" spans="1:63" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="31"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="20">
         <f>SUM(C10:C47)</f>
         <v>10396914</v>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>1253819</v>
+        <v>1253873</v>
       </c>
       <c r="F48" s="20">
         <f>SUM(F10:F47)</f>
-        <v>3917976</v>
+        <v>3918030</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" si="1"/>
-        <v>0.37684028164511124</v>
+        <v>0.37684547549397829</v>
       </c>
       <c r="H48" s="20">
         <f>SUM(H10:H47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>1452641</v>
+        <v>1452694</v>
       </c>
       <c r="K48" s="20">
         <f>SUM(K10:K47)</f>
-        <v>3929417</v>
+        <v>3929470</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.40922752312400446</v>
+        <v>0.40923304278728417</v>
       </c>
       <c r="M48" s="20">
         <f>SUM(M10:M47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>5094271</v>
+        <v>5094358</v>
       </c>
       <c r="P48" s="20">
         <f>SUM(P10:P47)</f>
-        <v>9212590</v>
+        <v>9212677</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.88598790990545484</v>
+        <v>0.88599627681944559</v>
       </c>
       <c r="R48" s="20">
         <f>SUM(R10:R47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>3085075</v>
+        <v>3085127</v>
       </c>
       <c r="U48" s="20">
         <f>SUM(U10:U47)</f>
-        <v>4004844</v>
+        <v>4004896</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.66611013948939546</v>
+        <v>0.66611878844732075</v>
       </c>
       <c r="W48" s="20">
         <f>SUM(W10:W47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2823472</v>
+        <v>2823529</v>
       </c>
       <c r="Z48" s="20">
         <f>SUM(Z10:Z47)</f>
-        <v>4037129</v>
+        <v>4037186</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.69478526709913957</v>
+        <v>0.69479507673371521</v>
       </c>
       <c r="AB48" s="20">
         <f>SUM(AB10:AB47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>3618419</v>
+        <v>3618519</v>
       </c>
       <c r="AE48" s="20">
         <f>SUM(AE10:AE47)</f>
-        <v>9489441</v>
+        <v>9489541</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.87452177245132845</v>
+        <v>0.87453098818671748</v>
       </c>
       <c r="AG48" s="20">
         <f>SUM(AG10:AG47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2580225</v>
+        <v>2580283</v>
       </c>
       <c r="AJ48" s="20">
         <f>SUM(AJ10:AJ47)</f>
-        <v>4110457</v>
+        <v>4110515</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.75240458978007696</v>
+        <v>0.75241520647457283</v>
       </c>
       <c r="AL48" s="20">
         <f>SUM(AL10:AL47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2523334</v>
+        <v>2523390</v>
       </c>
       <c r="AO48" s="20">
         <f>SUM(AO10:AO47)</f>
-        <v>4159204</v>
+        <v>4159260</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.77767365260951959</v>
+        <v>0.77768412329683057</v>
       </c>
       <c r="AQ48" s="20">
         <f>SUM(AQ10:AQ47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2270820</v>
+        <v>2270929</v>
       </c>
       <c r="AT48" s="20">
         <f>SUM(AT10:AT47)</f>
-        <v>9815892</v>
+        <v>9816001</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.89363626746529157</v>
+        <v>0.89364619079708385</v>
       </c>
       <c r="AV48" s="20">
         <f>SUM(AV10:AV47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="AX48" s="18">
         <f t="shared" si="18"/>
-        <v>2882356</v>
+        <v>2882430</v>
       </c>
       <c r="AY48" s="20">
         <f>SUM(AY10:AY47)</f>
-        <v>5362629</v>
+        <v>5362703</v>
       </c>
       <c r="AZ48" s="19">
         <f t="shared" si="19"/>
-        <v>0.8563148607972918</v>
+        <v>0.85632667725890022</v>
       </c>
       <c r="BA48" s="20">
         <f>SUM(BA10:BA47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BC48" s="18">
         <f t="shared" si="20"/>
-        <v>2728272</v>
+        <v>2728346</v>
       </c>
       <c r="BD48" s="20">
         <f>SUM(BD10:BD47)</f>
-        <v>5477616</v>
+        <v>5477690</v>
       </c>
       <c r="BE48" s="19">
         <f t="shared" si="21"/>
-        <v>0.89260062382133176</v>
+        <v>0.89261268243335623</v>
       </c>
       <c r="BF48" s="20">
         <f>SUM(BF10:BF47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="BH48" s="18">
         <f t="shared" si="22"/>
-        <v>4902614</v>
+        <v>4902704</v>
       </c>
       <c r="BI48" s="20">
         <f>SUM(BI10:BI47)</f>
-        <v>10081935</v>
+        <v>10082025</v>
       </c>
       <c r="BJ48" s="19">
         <f t="shared" si="23"/>
-        <v>0.9352806133595335</v>
+        <v>0.93528896247656335</v>
       </c>
       <c r="BK48"/>
     </row>
@@ -9390,17 +9390,22 @@
     <row r="55" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
       <c r="F57" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="W8:AA8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
@@ -9415,11 +9420,6 @@
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="W8:AA8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
